--- a/kaufpunkte_aktuell.xlsx
+++ b/kaufpunkte_aktuell.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>KP1: Mast +160% in 29 Tagen; Flag 8 Kalendertage, Range 1% der Masthöhe | KP2: Box 83.65–84.00; Breakout nur mit Vol &gt; Ø20d (8,615,809) gültig | KP3: MA50 aktuell 48.39 (nur bei intaktem Trend nutzen)</t>
+          <t>KP1: Mast +160% in 29 Tagen; Flag 8 Kalendertage, Range 1% der Masthöhe | KP2: Box 83.65–84.00; Breakout nur mit Vol &gt; Ø20d (8,615,810) gültig | KP3: MA50 aktuell 48.39 (nur bei intaktem Trend nutzen)</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 248.28–335.29; Breakout nur mit Vol &gt; Ø20d (332,029) gültig | KP2: Range 257.75–289.40; Berührungen oben 2, unten 3; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 280.09 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 248.28–335.29; Breakout nur mit Vol &gt; Ø20d (332,030) gültig | KP2: Range 257.75–289.40; Berührungen oben 2, unten 3; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 280.09 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 21.44–25.95; Breakout nur mit Vol &gt; Ø20d (702,277) gültig | KP2: MA50 aktuell 20.04 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 25.95</t>
+          <t>KP1: Box 21.44–25.95; Breakout nur mit Vol &gt; Ø20d (702,275) gültig | KP2: MA50 aktuell 20.04 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 25.95</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 69.29–85.73; Breakout nur mit Vol &gt; Ø20d (475,514) gültig | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 75.68 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 69.29–85.73; Breakout nur mit Vol &gt; Ø20d (475,515) gültig | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 75.68 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 211.88–293.51; Breakout nur mit Vol &gt; Ø20d (191,664) gültig | KP2: MA50 aktuell 245.75; Kauf erst wenn Schlusskurs drüber | KP3: 52W-Hoch 293.51 | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
+          <t>KP1: Box 211.88–293.51; Breakout nur mit Vol &gt; Ø20d (191,665) gültig | KP2: MA50 aktuell 245.75; Kauf erst wenn Schlusskurs drüber | KP3: 52W-Hoch 293.51 | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="X9" s="2" t="n">
-        <v>130.02</v>
+        <v>130.06</v>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 49.65–74.60; Breakout nur mit Vol &gt; Ø20d (1,235,156) gültig | KP2: MA50 aktuell 56.08; Kauf erst wenn Schlusskurs drüber | KP3: 52W-Hoch 74.60 | TT fehlt: Kurs &gt; MA50; ≤25 % unter 52W-Hoch; RS-Rank ≥ 70</t>
+          <t>KP1: Box 49.65–74.60; Breakout nur mit Vol &gt; Ø20d (1,235,155) gültig | KP2: MA50 aktuell 56.08; Kauf erst wenn Schlusskurs drüber | KP3: 52W-Hoch 74.60 | TT fehlt: Kurs &gt; MA50; ≤25 % unter 52W-Hoch; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>82.75</v>
+        <v>82.7</v>
       </c>
       <c r="AA13" s="2" t="inlineStr"/>
       <c r="AB13" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 60.13–67.53; Breakout nur mit Vol &gt; Ø20d (991,362) gültig | KP2: MA50 aktuell 56.83 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 67.53 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 60.13–67.53; Breakout nur mit Vol &gt; Ø20d (991,365) gültig | KP2: MA50 aktuell 56.83 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 67.53 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 292.17–326.63; Breakout nur mit Vol &gt; Ø20d (444,904) gültig | KP2: MA50 aktuell 266.95 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 326.63 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 292.17–326.63; Breakout nur mit Vol &gt; Ø20d (444,905) gültig | KP2: MA50 aktuell 266.95 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 326.63 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 22.88–29.80; Breakout nur mit Vol &gt; Ø20d (2,508,161) gültig | KP2: MA50 aktuell 22.26 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 29.80 | TT fehlt: MA200 steigt (≥1 Monat); RS-Rank ≥ 70</t>
+          <t>KP1: Box 22.88–29.80; Breakout nur mit Vol &gt; Ø20d (2,508,220) gültig | KP2: MA50 aktuell 22.26 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 29.80 | TT fehlt: MA200 steigt (≥1 Monat); RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 22.38–25.75; Breakout nur mit Vol &gt; Ø20d (3,203,171) gültig | KP2: MA50 aktuell 21.74 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 25.75 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 22.38–25.75; Breakout nur mit Vol &gt; Ø20d (3,203,325) gültig | KP2: MA50 aktuell 21.74 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 25.75 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 154.02–195.71; Breakout nur mit Vol &gt; Ø20d (647,012) gültig | KP2: MA50 aktuell 143.20 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 195.71 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 154.02–195.71; Breakout nur mit Vol &gt; Ø20d (647,015) gültig | KP2: MA50 aktuell 143.20 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 195.71 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
         <v>26.88</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>41.51</v>
+        <v>41.52</v>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 95.58–102.05; Breakout nur mit Vol &gt; Ø20d (512,732) gültig | KP2: MA50 aktuell 88.40 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 102.05 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 95.58–102.05; Breakout nur mit Vol &gt; Ø20d (512,730) gültig | KP2: MA50 aktuell 88.40 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 102.05 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 55.47–68.02; Breakout nur mit Vol &gt; Ø20d (1,260,441) gültig | KP2: MA50 aktuell 57.24 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 68.02 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 55.47–68.02; Breakout nur mit Vol &gt; Ø20d (1,260,440) gültig | KP2: MA50 aktuell 57.24 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 68.02 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -4953,14 +4953,14 @@
         <v>89.03</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>90.89</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>16.51</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="L39" s="3" t="n">
-        <v>90.98</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>84.53</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="O39" s="3" t="inlineStr"/>
       <c r="P39" s="3" t="inlineStr">
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="X39" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 90.89 | KP2: MA50 aktuell 69.90 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
+          <t>KP1: 52W-Hoch 90.90 | KP2: MA50 aktuell 69.90 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
         </is>
       </c>
       <c r="T79" s="4" t="n">
-        <v>216.01</v>
+        <v>216.02</v>
       </c>
       <c r="U79" s="4" t="inlineStr"/>
       <c r="V79" s="4" t="inlineStr">

--- a/kaufpunkte_aktuell.xlsx
+++ b/kaufpunkte_aktuell.xlsx
@@ -756,7 +756,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 21.49–28.50; Breakout nur mit Volumen über Ø50d (325,209) gültig | KP2: Range 21.21–24.62; Berührungen oben 2, unten 3; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 23.46 (nur bei intaktem Trend nutzen)</t>
+          <t>KP1: Box 21.49–28.50; Breakout nur mit Volumen über Ø50d (325,978) gültig | KP2: Range 21.21–24.62; Berührungen oben 2, unten 3; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 23.46 (nur bei intaktem Trend nutzen)</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>KP1: Kontraktionen: 33% → 14% → 15% → 16% → 16% → 9%; Pivot 91.10; Breakout braucht Vol ≥ 140% vom Ø | KP2: Box 82.53–91.10; Breakout nur mit Volumen über Ø50d (1,961,239) gültig | KP3: MA50 aktuell 73.25 (nur bei intaktem Trend nutzen)</t>
+          <t>KP1: Kontraktionen: 33% → 14% → 15% → 16% → 16% → 9%; Pivot 91.10; Breakout braucht Vol ≥ 140% vom Ø | KP2: Box 82.53–91.10; Breakout nur mit Volumen über Ø50d (1,961,244) gültig | KP3: MA50 aktuell 73.25 (nur bei intaktem Trend nutzen)</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 30.65–34.14; Breakout nur mit Volumen über Ø50d (466,966) gültig | KP2: Range 30.65–33.47; Berührungen oben 4, unten 2; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 32.04 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 30.65–34.14; Breakout nur mit Volumen über Ø50d (467,118) gültig | KP2: Range 30.65–33.47; Berührungen oben 4, unten 2; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 32.04 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 15.81–18.98; Breakout nur mit Volumen über Ø50d (2,302,462) gültig | KP2: Range 15.58–16.99; Berührungen oben 3, unten 5; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 16.45; Kauf erst wenn Schlusskurs drüber | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
+          <t>KP1: Box 15.81–18.98; Breakout nur mit Volumen über Ø50d (2,302,772) gültig | KP2: Range 15.58–16.99; Berührungen oben 3, unten 5; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 16.45; Kauf erst wenn Schlusskurs drüber | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 83.49–87.50; Breakout nur mit Volumen über Ø50d (400,480) gültig | KP2: Range 80.16–84.14; Berührungen oben 2, unten 2; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 82.50 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 83.49–87.50; Breakout nur mit Volumen über Ø50d (401,424) gültig | KP2: Range 80.16–84.14; Berührungen oben 2, unten 2; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 82.50 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 14.83–21.45; Breakout nur mit Volumen über Ø50d (1,749,306) gültig | KP2: Range 15.02–18.37; Berührungen oben 4, unten 4; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 16.53; Kauf erst wenn Schlusskurs drüber | TT fehlt: Kurs &gt; MA50; ≤25 % unter 52W-Hoch; RS-Rank ≥ 70</t>
+          <t>KP1: Box 14.83–21.45; Breakout nur mit Volumen über Ø50d (1,750,138) gültig | KP2: Range 15.02–18.37; Berührungen oben 4, unten 4; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 16.53; Kauf erst wenn Schlusskurs drüber | TT fehlt: Kurs &gt; MA50; ≤25 % unter 52W-Hoch; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>✗ +23%</t>
+          <t>✗ +24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+25%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 104.68–123.24; Breakout nur mit Volumen über Ø50d (118,021) gültig | KP2: Range 93.70–113.57; Berührungen oben 4, unten 2; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 105.66 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 104.68–123.24; Breakout nur mit Volumen über Ø50d (118,222) gültig | KP2: Range 93.70–113.57; Berührungen oben 4, unten 2; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 105.66 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 22.38–25.75; Breakout nur mit Volumen über Ø50d (3,660,049) gültig | KP2: Range 21.51–24.38; Berührungen oben 2, unten 2; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 21.79 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 22.38–25.75; Breakout nur mit Volumen über Ø50d (3,668,422) gültig | KP2: Range 21.51–24.38; Berührungen oben 2, unten 2; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 21.79 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 30.85–36.27; Breakout nur mit Volumen über Ø50d (935,923) gültig | KP2: MA50 aktuell 31.71 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 36.27</t>
+          <t>KP1: Box 30.85–36.27; Breakout nur mit Volumen über Ø50d (939,702) gültig | KP2: MA50 aktuell 31.71 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 36.27</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 33.40–35.14; Breakout nur mit Volumen über Ø50d (388,285) gültig | KP2: MA50 aktuell 31.15 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 35.14</t>
+          <t>KP1: Box 33.40–35.14; Breakout nur mit Volumen über Ø50d (389,952) gültig | KP2: MA50 aktuell 31.15 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 35.14</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 67.43–77.00; Breakout nur mit Volumen über Ø50d (1,074,002) gültig | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 66.02 (nur bei intaktem Trend nutzen)</t>
+          <t>KP1: Box 67.43–77.00; Breakout nur mit Volumen über Ø50d (1,074,006) gültig | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 66.02 (nur bei intaktem Trend nutzen)</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 370.74–458.25; Breakout nur mit Volumen über Ø50d (601,794) gültig | KP2: MA50 aktuell 339.07 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 458.25</t>
+          <t>KP1: Box 370.74–458.25; Breakout nur mit Volumen über Ø50d (601,804) gültig | KP2: MA50 aktuell 339.07 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 458.25</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="T19" s="2" t="n">
-        <v>259.25</v>
+        <v>259.24</v>
       </c>
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 90.51–96.99; Breakout nur mit Volumen über Ø50d (607,883) gültig | KP2: MA50 aktuell 84.27 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 96.99</t>
+          <t>KP1: Box 90.51–96.99; Breakout nur mit Volumen über Ø50d (608,194) gültig | KP2: MA50 aktuell 84.27 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 96.99</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="X23" s="2" t="n">
-        <v>83.54000000000001</v>
+        <v>83.55</v>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 107.76–135.00; Breakout nur mit Volumen über Ø50d (258,659) gültig | KP2: MA50 aktuell 101.20 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 135.00</t>
+          <t>KP1: Box 107.76–135.00; Breakout nur mit Volumen über Ø50d (258,690) gültig | KP2: MA50 aktuell 101.20 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 135.00</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 132.00–143.29; Breakout nur mit Volumen über Ø50d (729,795) gültig | KP2: MA50 aktuell 119.55 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 143.29</t>
+          <t>KP1: Box 132.00–143.29; Breakout nur mit Volumen über Ø50d (730,038) gültig | KP2: MA50 aktuell 119.55 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 143.29</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 93.72–100.75; Breakout nur mit Volumen über Ø50d (1,890,898) gültig | KP2: MA50 aktuell 90.85 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 100.75</t>
+          <t>KP1: Box 93.72–100.75; Breakout nur mit Volumen über Ø50d (1,891,308) gültig | KP2: MA50 aktuell 90.85 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 100.75</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 54.87–60.10; Breakout nur mit Volumen über Ø50d (1,832,961) gültig | KP2: MA50 aktuell 53.08 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 60.10</t>
+          <t>KP1: Box 54.87–60.10; Breakout nur mit Volumen über Ø50d (1,837,208) gültig | KP2: MA50 aktuell 53.08 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 60.10</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 21.05–24.50; Breakout nur mit Volumen über Ø50d (135,997) gültig | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 20.95 (nur bei intaktem Trend nutzen)</t>
+          <t>KP1: Box 21.05–24.50; Breakout nur mit Volumen über Ø50d (136,066) gültig | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 20.95 (nur bei intaktem Trend nutzen)</t>
         </is>
       </c>
     </row>
@@ -5925,18 +5925,18 @@
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>95.36</v>
+        <v>96</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>+3.8%</t>
+          <t>+4.5%</t>
         </is>
       </c>
       <c r="N47" s="2" t="n">
         <v>87.06</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>103.64</v>
+        <v>104.92</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>KP1: Range 87.07–95.35; Berührungen oben 3, unten 5; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 106.15 | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Range 87.07–95.99; Berührungen oben 4, unten 5; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 106.15 | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -6978,18 +6978,18 @@
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>144.36</v>
+        <v>144.55</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="N56" s="2" t="n">
         <v>127.42</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>161.28</v>
+        <v>161.66</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>KP1: Range 127.43–144.35; Berührungen oben 2, unten 2; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 160.47 | KP3: Hoch der letzten 20 Handelstage | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
+          <t>KP1: Range 127.43–144.54; Berührungen oben 2, unten 2; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 160.47 | KP3: Hoch der letzten 20 Handelstage | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -7666,12 +7666,12 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>✗ +23%</t>
+          <t>✗ +18%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-58%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -8017,12 +8017,12 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>✗ +21%</t>
+          <t>✓ +97%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>-26%</t>
+          <t>-36%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -8039,7 +8039,7 @@
         </is>
       </c>
       <c r="N65" s="2" t="n">
-        <v>54.05</v>
+        <v>54.06</v>
       </c>
       <c r="O65" s="2" t="n">
         <v>59.92</v>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>KP1: Range 54.06–56.99; Berührungen oben 5, unten 8; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 58.45 | KP3: MA50 aktuell 55.64; Kauf erst wenn Schlusskurs drüber | TT fehlt: Kurs &gt; MA50; ≥25 % über 52W-Tief; RS-Rank ≥ 70</t>
+          <t>KP1: Range 54.07–56.99; Berührungen oben 5, unten 8; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 58.45 | KP3: MA50 aktuell 55.64; Kauf erst wenn Schlusskurs drüber | TT fehlt: Kurs &gt; MA50; ≥25 % über 52W-Tief; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 48.47–51.73; Breakout nur mit Volumen über Ø50d (137,328) gültig | KP2: MA50 aktuell 48.19 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 51.73 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 48.47–51.73; Breakout nur mit Volumen über Ø50d (137,758) gültig | KP2: MA50 aktuell 48.19 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 51.73 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 56.28–59.50; Breakout nur mit Volumen über Ø50d (7,093,211) gültig | KP2: MA50 aktuell 54.53 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 59.50 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 56.28–59.50; Breakout nur mit Volumen über Ø50d (7,180,184) gültig | KP2: MA50 aktuell 54.53 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 59.50 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 44.72–50.26; Breakout nur mit Volumen über Ø50d (173,606) gültig | KP2: MA50 aktuell 45.96 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 50.26 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 44.72–50.26; Breakout nur mit Volumen über Ø50d (173,628) gültig | KP2: MA50 aktuell 45.96 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 50.26 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 29.20–31.25; Breakout nur mit Volumen über Ø50d (363,127) gültig | KP2: MA50 aktuell 28.88 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 31.25 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 29.20–31.25; Breakout nur mit Volumen über Ø50d (363,310) gültig | KP2: MA50 aktuell 28.88 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 31.25 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -10246,18 +10246,18 @@
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>40.26</v>
+        <v>40.33</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="n">
         <v>37.8</v>
       </c>
       <c r="O84" s="2" t="n">
-        <v>42.71</v>
+        <v>42.84</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>KP1: Range 37.81–40.25; Berührungen oben 6, unten 5; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 41.00 | KP3: MA50 aktuell 39.26 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Range 37.81–40.32; Berührungen oben 6, unten 5; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 41.00 | KP3: MA50 aktuell 39.26 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -10700,12 +10700,12 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>✗ +15%</t>
+          <t>✗ +18%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+51%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 1140.74–1249.45; Breakout nur mit Volumen über Ø50d (2,971,349) gültig | KP2: MA50 aktuell 1147.32 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 1249.45 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 1140.74–1249.45; Breakout nur mit Volumen über Ø50d (2,971,378) gültig | KP2: MA50 aktuell 1147.32 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 1249.45 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 565.10–677.90; Breakout nur mit Volumen über Ø50d (344,544) gültig | KP2: MA50 aktuell 504.31 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 677.90 | TT fehlt: MA150 &gt; MA200; MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
+          <t>KP1: Box 565.10–677.90; Breakout nur mit Volumen über Ø50d (344,676) gültig | KP2: MA50 aktuell 504.31 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 677.90 | TT fehlt: MA150 &gt; MA200; MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -11357,7 +11357,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 92.95–100.34; Breakout nur mit Volumen über Ø50d (5,759,319) gültig | KP2: MA50 aktuell 93.48 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 100.34 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 92.95–100.34; Breakout nur mit Volumen über Ø50d (5,759,332) gültig | KP2: MA50 aktuell 93.48 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 100.34 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 175.08–191.60; Breakout nur mit Volumen über Ø50d (1,113,753) gültig | KP2: MA50 aktuell 175.99 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 191.60 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 175.08–191.60; Breakout nur mit Volumen über Ø50d (1,114,566) gültig | KP2: MA50 aktuell 175.99 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 191.60 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -11862,12 +11862,12 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>✓ +54%</t>
+          <t>✓ +53%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>-60%</t>
+          <t>+98%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 60.21–64.61; Breakout nur mit Volumen über Ø50d (3,268,376) gültig | KP2: MA50 aktuell 56.76 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 64.61 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 60.21–64.61; Breakout nur mit Volumen über Ø50d (3,277,834) gültig | KP2: MA50 aktuell 56.76 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 64.61 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 42.83–55.00; Breakout nur mit Volumen über Ø50d (243,249) gültig | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 46.32; Kauf erst wenn Schlusskurs drüber | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
+          <t>KP1: Box 42.83–55.00; Breakout nur mit Volumen über Ø50d (244,418) gültig | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 46.32; Kauf erst wenn Schlusskurs drüber | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -12677,12 +12677,12 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>✗ +18%</t>
+          <t>✗ +19%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>+26%</t>
+          <t>+48%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 232.03–245.00; Breakout nur mit Volumen über Ø50d (365,022) gültig | KP2: MA50 aktuell 219.23 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 245.00 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 232.03–245.00; Breakout nur mit Volumen über Ø50d (366,910) gültig | KP2: MA50 aktuell 219.23 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 245.00 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -13377,12 +13377,12 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>✓ +38%</t>
+          <t>✓ +72%</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+406%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -13845,12 +13845,12 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>✓ +46%</t>
+          <t>✓ +78%</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>+254%</t>
+          <t>+383%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -13976,7 +13976,7 @@
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>67.48</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>62.24</v>
       </c>
       <c r="O116" s="2" t="n">
-        <v>72.70999999999999</v>
+        <v>72.73</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>KP1: Range 62.25–67.47; Berührungen oben 3, unten 3; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 70.29 | KP3: MA50 aktuell 61.13 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Range 62.25–67.48; Berührungen oben 3, unten 3; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 70.29 | KP3: MA50 aktuell 61.13 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -14093,7 +14093,7 @@
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>41.87</v>
+        <v>41.88</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>38.64</v>
       </c>
       <c r="O117" s="2" t="n">
-        <v>45.08</v>
+        <v>45.1</v>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>KP1: Range 38.65–41.86; Berührungen oben 3, unten 3; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 43.81 | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Range 38.65–41.87; Berührungen oben 3, unten 3; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 43.81 | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -14547,12 +14547,12 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>✗ +24%</t>
+          <t>✓ +63%</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>+101%</t>
+          <t>+259%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -14686,10 +14686,10 @@
         </is>
       </c>
       <c r="N122" s="2" t="n">
-        <v>66.95</v>
+        <v>66.38</v>
       </c>
       <c r="O122" s="2" t="n">
-        <v>73.97</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>KP1: Range 66.96–70.46; Berührungen oben 7, unten 6; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 71.47 | KP3: Hoch der letzten 20 Handelstage | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
+          <t>KP1: Range 66.39–70.46; Berührungen oben 7, unten 6; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 71.47 | KP3: Hoch der letzten 20 Handelstage | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 95.58–102.05; Breakout nur mit Volumen über Ø50d (487,122) gültig | KP2: MA50 aktuell 89.91 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 102.05 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 95.58–102.05; Breakout nur mit Volumen über Ø50d (487,842) gültig | KP2: MA50 aktuell 89.91 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 102.05 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>+98%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="AC128" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 55.47–68.02; Breakout nur mit Volumen über Ø50d (1,253,738) gültig | KP2: MA50 aktuell 57.82 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 68.02 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 55.47–68.02; Breakout nur mit Volumen über Ø50d (1,253,740) gültig | KP2: MA50 aktuell 57.82 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 68.02 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -15947,12 +15947,12 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>✓ +48%</t>
+          <t>✓ +57%</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+65%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="AC134" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 67.75–73.34; Breakout nur mit Volumen über Ø50d (1,697,932) gültig | KP2: MA50 aktuell 67.27 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 73.34 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 67.75–73.34; Breakout nur mit Volumen über Ø50d (1,697,934) gültig | KP2: MA50 aktuell 67.27 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 73.34 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -16179,12 +16179,12 @@
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>✓ +39%</t>
+          <t>✓ +45%</t>
         </is>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>+26%</t>
+          <t>+171%</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr">
@@ -17309,7 +17309,7 @@
         <v>60.33</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>60.77</v>
+        <v>60.78</v>
       </c>
       <c r="E145" s="3" t="n">
         <v>23.34</v>
@@ -17343,7 +17343,7 @@
         </is>
       </c>
       <c r="L145" s="3" t="n">
-        <v>60.83</v>
+        <v>60.84</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         </is>
       </c>
       <c r="N145" s="3" t="n">
-        <v>56.52</v>
+        <v>56.53</v>
       </c>
       <c r="O145" s="3" t="inlineStr"/>
       <c r="P145" s="3" t="inlineStr">
@@ -17387,11 +17387,11 @@
         </is>
       </c>
       <c r="X145" s="3" t="n">
-        <v>60.78</v>
+        <v>60.79</v>
       </c>
       <c r="Y145" s="3" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>+0.8%</t>
         </is>
       </c>
       <c r="Z145" s="3" t="n">
@@ -17405,7 +17405,7 @@
       </c>
       <c r="AC145" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 60.77 | KP2: MA50 aktuell 53.19 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
+          <t>KP1: 52W-Hoch 60.78 | KP2: MA50 aktuell 53.19 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>
@@ -17539,14 +17539,14 @@
         <v>254.14</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>260</v>
+        <v>260.79</v>
       </c>
       <c r="E147" s="3" t="n">
         <v>99.61</v>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="G147" s="3" t="n">
@@ -17573,15 +17573,15 @@
         </is>
       </c>
       <c r="L147" s="3" t="n">
-        <v>260.26</v>
+        <v>261.05</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="N147" s="3" t="n">
-        <v>241.8</v>
+        <v>242.53</v>
       </c>
       <c r="O147" s="3" t="inlineStr"/>
       <c r="P147" s="3" t="inlineStr">
@@ -17617,11 +17617,11 @@
         </is>
       </c>
       <c r="X147" s="3" t="n">
-        <v>260.01</v>
+        <v>260.8</v>
       </c>
       <c r="Y147" s="3" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>+2.6%</t>
         </is>
       </c>
       <c r="Z147" s="3" t="n">
@@ -17635,7 +17635,7 @@
       </c>
       <c r="AC147" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 260.00 | KP2: MA50 aktuell 208.11 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
+          <t>KP1: 52W-Hoch 260.79 | KP2: MA50 aktuell 208.11 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>✓ +41%</t>
+          <t>✓ +50%</t>
         </is>
       </c>
       <c r="J152" s="3" t="inlineStr">
@@ -19629,12 +19629,12 @@
       </c>
       <c r="I165" s="3" t="inlineStr">
         <is>
-          <t>✓ +77%</t>
+          <t>✓ +49%</t>
         </is>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+784%</t>
         </is>
       </c>
       <c r="K165" s="3" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t>✓ +26%</t>
+          <t>✗ +25%</t>
         </is>
       </c>
       <c r="J172" s="4" t="inlineStr">
@@ -21190,7 +21190,7 @@
         </is>
       </c>
       <c r="Z178" s="4" t="n">
-        <v>243.33</v>
+        <v>243.29</v>
       </c>
       <c r="AA178" s="4" t="inlineStr"/>
       <c r="AB178" s="4" t="inlineStr">
@@ -21354,12 +21354,12 @@
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t>✗ +17%</t>
+          <t>✓ +27%</t>
         </is>
       </c>
       <c r="J180" s="4" t="inlineStr">
         <is>
-          <t>+88%</t>
+          <t>+171%</t>
         </is>
       </c>
       <c r="K180" s="4" t="inlineStr">
@@ -21449,7 +21449,7 @@
         <v>400.58</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>413.24</v>
+        <v>413.25</v>
       </c>
       <c r="E181" s="4" t="n">
         <v>230.45</v>
@@ -21527,7 +21527,7 @@
         </is>
       </c>
       <c r="X181" s="4" t="n">
-        <v>413.25</v>
+        <v>413.26</v>
       </c>
       <c r="Y181" s="4" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="AC181" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 413.24 | KP2: MA50 aktuell 371.60 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 413.25 | KP2: MA50 aktuell 371.60 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -22044,12 +22044,12 @@
       </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t>✓ +26%</t>
+          <t>✗ +23%</t>
         </is>
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
-          <t>+360%</t>
+          <t>+197%</t>
         </is>
       </c>
       <c r="K186" s="4" t="inlineStr">
@@ -27830,11 +27830,11 @@
         </is>
       </c>
       <c r="R236" s="4" t="n">
-        <v>321.55</v>
+        <v>323.06</v>
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="T236" s="4" t="n">
@@ -27848,29 +27848,29 @@
       </c>
       <c r="W236" s="4" t="inlineStr">
         <is>
-          <t>Fallback: Quartals-Hoch (63 Tage)</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="X236" s="4" t="n">
-        <v>329.68</v>
+        <v>320.69</v>
       </c>
       <c r="Y236" s="4" t="inlineStr">
         <is>
-          <t>+2.6%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="Z236" s="4" t="n">
-        <v>303.3</v>
+        <v>303.14</v>
       </c>
       <c r="AA236" s="4" t="inlineStr"/>
       <c r="AB236" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — mittelfristiger Widerstand</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="AC236" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 362.41 | KP2: Hoch der letzten 20 Handelstage | KP3: Hoch der letzten 63 Handelstage | TT fehlt: Kurs &gt; MA150 &amp; MA200; MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 362.41 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 319.10 (nur bei intaktem Trend nutzen) | TT fehlt: Kurs &gt; MA150 &amp; MA200; MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -28024,12 +28024,12 @@
       </c>
       <c r="I238" s="4" t="inlineStr">
         <is>
-          <t>✓ +74%</t>
+          <t>✓ +32%</t>
         </is>
       </c>
       <c r="J238" s="4" t="inlineStr">
         <is>
-          <t>+22%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K238" s="4" t="inlineStr">
@@ -28183,7 +28183,7 @@
         </is>
       </c>
       <c r="T239" s="4" t="n">
-        <v>50.05</v>
+        <v>50.06</v>
       </c>
       <c r="U239" s="4" t="inlineStr"/>
       <c r="V239" s="4" t="inlineStr">
@@ -28949,7 +28949,7 @@
       </c>
       <c r="J246" s="4" t="inlineStr">
         <is>
-          <t>+73%</t>
+          <t>+72%</t>
         </is>
       </c>
       <c r="K246" s="4" t="inlineStr">
@@ -29174,12 +29174,12 @@
       </c>
       <c r="I248" s="4" t="inlineStr">
         <is>
-          <t>✗ +18%</t>
+          <t>✗ +19%</t>
         </is>
       </c>
       <c r="J248" s="4" t="inlineStr">
         <is>
-          <t>+75%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K248" s="4" t="inlineStr">
@@ -29188,7 +29188,7 @@
         </is>
       </c>
       <c r="L248" s="4" t="n">
-        <v>48.8</v>
+        <v>48.81</v>
       </c>
       <c r="M248" s="4" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         </is>
       </c>
       <c r="N248" s="4" t="n">
-        <v>45.34</v>
+        <v>45.35</v>
       </c>
       <c r="O248" s="4" t="inlineStr"/>
       <c r="P248" s="4" t="inlineStr">
@@ -29384,7 +29384,7 @@
         <v>161.77</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>164.32</v>
+        <v>164.37</v>
       </c>
       <c r="E250" s="4" t="n">
         <v>83.12</v>
@@ -29418,7 +29418,7 @@
         </is>
       </c>
       <c r="L250" s="4" t="n">
-        <v>164.49</v>
+        <v>164.53</v>
       </c>
       <c r="M250" s="4" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         </is>
       </c>
       <c r="N250" s="4" t="n">
-        <v>152.82</v>
+        <v>152.86</v>
       </c>
       <c r="O250" s="4" t="inlineStr"/>
       <c r="P250" s="4" t="inlineStr">
@@ -29462,7 +29462,7 @@
         </is>
       </c>
       <c r="X250" s="4" t="n">
-        <v>164.33</v>
+        <v>164.38</v>
       </c>
       <c r="Y250" s="4" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
       </c>
       <c r="AC250" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 164.32 | KP2: MA50 aktuell 139.06 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 164.37 | KP2: MA50 aktuell 139.06 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="I260" s="4" t="inlineStr">
         <is>
-          <t>✗ +13%</t>
+          <t>✗ +12%</t>
         </is>
       </c>
       <c r="J260" s="4" t="inlineStr">

--- a/kaufpunkte_aktuell.xlsx
+++ b/kaufpunkte_aktuell.xlsx
@@ -873,7 +873,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 157.11–176.58; Breakout nur mit Volumen über Ø50d (2,679,099) gültig | KP2: Range 142.86–171.74; Berührungen oben 4, unten 2; Ziel = Ausbruch + Rechteckhöhe | KP3: Hoch der letzten 20 Handelstage</t>
+          <t>KP1: Box 157.11–176.58; Breakout nur mit Volumen über Ø50d (2,679,100) gültig | KP2: Range 142.86–171.74; Berührungen oben 4, unten 2; Ziel = Ausbruch + Rechteckhöhe | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 77 Wochen von 2025-02-21 bis 2026-08-14; Cup-Tiefe 55 %, Rücksetzer 17 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.76; Ziel = Kaufpunkt plus Cup-Höhe | KP2: Box 176.82–191.62; Breakout nur mit Volumen über Ø50d (821,332) gültig | KP3: MA50 aktuell 162.33 (nur bei intaktem Trend nutzen)</t>
+          <t>KP1: Giant Base auf Wochenbasis, 77 Wochen von 2025-02-21 bis 2026-08-14; Cup-Tiefe 55 %, Rücksetzer 17 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.76; Ziel = Kaufpunkt plus Cup-Höhe | KP2: Box 176.82–191.62; Breakout nur mit Volumen über Ø50d (821,364) gültig | KP3: MA50 aktuell 162.33 (nur bei intaktem Trend nutzen)</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 56 Wochen von 2025-05-16 bis 2026-06-12; Cup-Tiefe 43 %, Rücksetzer 38 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.85; Ziel = Kaufpunkt plus Cup-Höhe | KP2: Box 69.43–75.40; Breakout nur mit Volumen über Ø50d (799,271) gültig | KP3: MA50 aktuell 66.07 (nur bei intaktem Trend nutzen)</t>
+          <t>KP1: Giant Base auf Wochenbasis, 56 Wochen von 2025-05-16 bis 2026-06-12; Cup-Tiefe 43 %, Rücksetzer 38 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.85; Ziel = Kaufpunkt plus Cup-Höhe | KP2: Box 69.43–75.40; Breakout nur mit Volumen über Ø50d (799,270) gültig | KP3: MA50 aktuell 66.07 (nur bei intaktem Trend nutzen)</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 36 Wochen von 2025-12-12 bis 2026-08-21; Cup-Tiefe 35 %, Rücksetzer 28 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.58; Ziel = Kaufpunkt plus Cup-Höhe | KP2: Box 22.97–25.33; Breakout nur mit Volumen über Ø50d (410,107) gültig | KP3: MA50 aktuell 20.08 (nur bei intaktem Trend nutzen) | TT fehlt: MA150 &gt; MA200; RS-Rank ≥ 70</t>
+          <t>KP1: Giant Base auf Wochenbasis, 36 Wochen von 2025-12-12 bis 2026-08-21; Cup-Tiefe 35 %, Rücksetzer 28 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.58; Ziel = Kaufpunkt plus Cup-Höhe | KP2: Box 22.97–25.33; Breakout nur mit Volumen über Ø50d (410,106) gültig | KP3: MA50 aktuell 20.08 (nur bei intaktem Trend nutzen) | TT fehlt: MA150 &gt; MA200; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 13 Wochen von 2026-05-22 bis 2026-08-21; Cup-Tiefe 24 %, Rücksetzer 42 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.79; Ziel = Kaufpunkt plus Cup-Höhe | KP2: Box 30.13–33.40; Breakout nur mit Volumen über Ø50d (7,312,756) gültig | KP3: MA50 aktuell 28.40 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Giant Base auf Wochenbasis, 13 Wochen von 2026-05-22 bis 2026-08-21; Cup-Tiefe 24 %, Rücksetzer 42 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.79; Ziel = Kaufpunkt plus Cup-Höhe | KP2: Box 30.13–33.40; Breakout nur mit Volumen über Ø50d (7,315,526) gültig | KP3: MA50 aktuell 28.40 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 58.96–69.98; Breakout nur mit Volumen über Ø50d (2,522,911) gültig | KP2: Range 57.95–64.49; Berührungen oben 2, unten 4; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 60.63 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 58.96–69.98; Breakout nur mit Volumen über Ø50d (2,522,914) gültig | KP2: Range 57.95–64.49; Berührungen oben 2, unten 4; Ziel = Ausbruch + Rechteckhöhe | KP3: MA50 aktuell 60.63 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>47.49</v>
+        <v>47.46</v>
       </c>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="T13" s="2" t="n">
-        <v>47.49</v>
+        <v>47.46</v>
       </c>
       <c r="U13" s="2" t="n">
         <v>63.79</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>KP1: Mast +114% in 24 Tagen; Flag 3 Kalendertage, Range 14% der Masthöhe | KP2: Giant Base auf Wochenbasis, 9 Wochen von 2026-06-26 bis 2026-08-28; Cup-Tiefe 35 %, Rücksetzer 29 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.92; Ziel = Kaufpunkt plus Cup-Höhe | KP3: MA50 aktuell 32.37 (nur bei intaktem Trend nutzen) | TT fehlt: MA150 &gt; MA200; RS-Rank ≥ 70</t>
+          <t>KP1: Mast +114% in 24 Tagen; Flag 3 Kalendertage, Range 14% der Masthöhe | KP2: Giant Base auf Wochenbasis, 9 Wochen von 2026-06-26 bis 2026-08-28; Cup-Tiefe 35 %, Rücksetzer 30 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.92; Ziel = Kaufpunkt plus Cup-Höhe | KP3: MA50 aktuell 32.37 (nur bei intaktem Trend nutzen) | TT fehlt: MA150 &gt; MA200; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 427.54–514.00; Breakout nur mit Volumen über Ø50d (6,515,310) gültig | KP2: MA50 aktuell 433.17 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 514.00</t>
+          <t>KP1: Box 427.54–514.00; Breakout nur mit Volumen über Ø50d (6,515,400) gültig | KP2: MA50 aktuell 433.17 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 514.00</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 64.98–87.03; Breakout nur mit Volumen über Ø50d (1,006,409) gültig | KP2: MA50 aktuell 71.34 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 87.03</t>
+          <t>KP1: Box 64.98–87.03; Breakout nur mit Volumen über Ø50d (1,006,962) gültig | KP2: MA50 aktuell 71.34 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 87.03</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 19.73–27.80; Breakout nur mit Volumen über Ø50d (1,550,036) gültig | KP2: MA50 aktuell 14.52 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 27.80</t>
+          <t>KP1: Box 19.73–27.80; Breakout nur mit Volumen über Ø50d (1,550,058) gültig | KP2: MA50 aktuell 14.52 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 27.80</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
         <v>191.23</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>194.53</v>
+        <v>194.54</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>83.12</v>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="R30" s="2" t="n">
-        <v>194.72</v>
+        <v>194.73</v>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="T30" s="2" t="n">
-        <v>180.91</v>
+        <v>180.92</v>
       </c>
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="X30" s="2" t="n">
-        <v>194.54</v>
+        <v>194.55</v>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="Z30" s="2" t="n">
-        <v>175.09</v>
+        <v>175.1</v>
       </c>
       <c r="AA30" s="2" t="inlineStr"/>
       <c r="AB30" s="2" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 23 Wochen von 2026-02-20 bis 2026-07-31; Cup-Tiefe 28 %, Rücksetzer 36 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.87; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 194.53 | KP3: Hoch der letzten 20 Handelstage</t>
+          <t>KP1: Giant Base auf Wochenbasis, 23 Wochen von 2026-02-20 bis 2026-07-31; Cup-Tiefe 28 %, Rücksetzer 36 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.87; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 194.54 | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="T56" s="2" t="n">
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>273.79</v>
+        <v>273.99</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
@@ -9354,14 +9354,14 @@
         </is>
       </c>
       <c r="N76" s="2" t="n">
-        <v>246.42</v>
+        <v>246.6</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>351.48</v>
+        <v>351.68</v>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>Score 86/100</t>
+          <t>Score 85/100</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 20 Wochen von 2026-04-10 bis 2026-08-28; Cup-Tiefe 28 %, Rücksetzer 14 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.85; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 285.67 | KP3: MA50 aktuell 224.11 (nur bei intaktem Trend nutzen) | TT fehlt: MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
+          <t>KP1: Giant Base auf Wochenbasis, 20 Wochen von 2026-04-10 bis 2026-08-28; Cup-Tiefe 28 %, Rücksetzer 15 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.85; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 285.67 | KP3: MA50 aktuell 224.11 (nur bei intaktem Trend nutzen) | TT fehlt: MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>✓ +39%</t>
+          <t>✓ +38%</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>Score 84/100</t>
+          <t>Score 83/100</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 19 Wochen von 2026-04-17 bis 2026-08-28; Cup-Tiefe 33 %, Rücksetzer 15 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.85; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 306.25 | KP3: MA50 aktuell 215.27 (nur bei intaktem Trend nutzen) | TT fehlt: MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
+          <t>KP1: Giant Base auf Wochenbasis, 19 Wochen von 2026-04-17 bis 2026-08-28; Cup-Tiefe 33 %, Rücksetzer 16 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.85; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 306.25 | KP3: MA50 aktuell 215.27 (nur bei intaktem Trend nutzen) | TT fehlt: MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>Score 78/100</t>
+          <t>Score 77/100</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -15609,7 +15609,7 @@
       </c>
       <c r="AC129" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 19 Wochen von 2026-04-17 bis 2026-08-28; Cup-Tiefe 34 %, Rücksetzer 22 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.75; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 165.76 | KP3: MA50 aktuell 122.66 (nur bei intaktem Trend nutzen) | TT fehlt: MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
+          <t>KP1: Giant Base auf Wochenbasis, 19 Wochen von 2026-04-17 bis 2026-08-28; Cup-Tiefe 34 %, Rücksetzer 26 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.75; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 165.76 | KP3: MA50 aktuell 122.66 (nur bei intaktem Trend nutzen) | TT fehlt: MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -15862,14 +15862,14 @@
         <v>95.76000000000001</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>98.3</v>
+        <v>98.52</v>
       </c>
       <c r="E132" s="3" t="n">
         <v>41.47</v>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="G132" s="3" t="n">
@@ -15896,15 +15896,15 @@
         </is>
       </c>
       <c r="L132" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>98.62</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>+3.0%</t>
         </is>
       </c>
       <c r="N132" s="3" t="n">
-        <v>91.42</v>
+        <v>91.62</v>
       </c>
       <c r="O132" s="3" t="inlineStr"/>
       <c r="P132" s="3" t="inlineStr">
@@ -15940,15 +15940,15 @@
         </is>
       </c>
       <c r="X132" s="3" t="n">
-        <v>98.31</v>
+        <v>98.53</v>
       </c>
       <c r="Y132" s="3" t="inlineStr">
         <is>
-          <t>+2.7%</t>
+          <t>+2.9%</t>
         </is>
       </c>
       <c r="Z132" s="3" t="n">
-        <v>88.48</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="AA132" s="3" t="inlineStr"/>
       <c r="AB132" s="3" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="AC132" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 98.30 | KP2: MA50 aktuell 84.03 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
+          <t>KP1: 52W-Hoch 98.52 | KP2: MA50 aktuell 84.03 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>

--- a/kaufpunkte_aktuell.xlsx
+++ b/kaufpunkte_aktuell.xlsx
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 12 Wochen von 2026-06-05 bis 2026-08-28; Cup-Tiefe 25 %, Rücksetzer 31 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.88; Ziel = Kaufpunkt plus Cup-Höhe | KP2: Box 66.42–71.93; Breakout nur mit Volumen über Ø50d (3,145,287) gültig | KP3: Range 56.72–67.79; Berührungen oben 3, unten 2; Ziel = Ausbruch + Rechteckhöhe | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Giant Base auf Wochenbasis, 12 Wochen von 2026-06-05 bis 2026-08-28; Cup-Tiefe 25 %, Rücksetzer 31 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.88; Ziel = Kaufpunkt plus Cup-Höhe | KP2: Box 66.42–71.93; Breakout nur mit Volumen über Ø50d (3,146,592) gültig | KP3: Range 56.72–67.79; Berührungen oben 3, unten 2; Ziel = Ausbruch + Rechteckhöhe | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>KP1: Kontraktionen: 17% → 18% → 17% → 12% → 11% → 11%; Pivot 24.52; Breakout braucht Vol ≥ 140% vom Ø | KP2: Box 22.13–24.52; Breakout nur mit Volumen über Ø50d (1,544,559) gültig | KP3: MA50 aktuell 19.07 (nur bei intaktem Trend nutzen)</t>
+          <t>KP1: Kontraktionen: 17% → 18% → 17% → 12% → 11% → 11%; Pivot 24.52; Breakout braucht Vol ≥ 140% vom Ø | KP2: Box 22.13–24.52; Breakout nur mit Volumen über Ø50d (1,545,036) gültig | KP3: MA50 aktuell 19.07 (nur bei intaktem Trend nutzen)</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 39 Wochen von 2025-10-03 bis 2026-07-03; Cup-Tiefe 38 %, Rücksetzer 36 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.94; Ziel = Kaufpunkt plus Cup-Höhe | KP2: Box 58.24–66.37; Breakout nur mit Volumen über Ø50d (601,171) gültig | KP3: MA50 aktuell 47.74 (nur bei intaktem Trend nutzen)</t>
+          <t>KP1: Giant Base auf Wochenbasis, 39 Wochen von 2025-10-03 bis 2026-07-03; Cup-Tiefe 38 %, Rücksetzer 36 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.94; Ziel = Kaufpunkt plus Cup-Höhe | KP2: Box 58.24–66.37; Breakout nur mit Volumen über Ø50d (601,812) gültig | KP3: MA50 aktuell 47.74 (nur bei intaktem Trend nutzen)</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 64.98–87.03; Breakout nur mit Volumen über Ø50d (994,772) gültig | KP2: Rückeroberung vor 6 Tag(en), Kontakt-Tief 78.32, Umkehrtag-Hoch 82.74 | KP3: Hoch der letzten 20 Handelstage</t>
+          <t>KP1: Box 64.98–87.03; Breakout nur mit Volumen über Ø50d (994,778) gültig | KP2: Rückeroberung vor 6 Tag(en), Kontakt-Tief 78.32, Umkehrtag-Hoch 82.74 | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 30 Wochen von 2026-01-30 bis 2026-08-28; Cup-Tiefe 44 %, Rücksetzer 38 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.53; Ziel = Kaufpunkt plus Cup-Höhe | KP2: Box 34.39–40.83; Breakout nur mit Volumen über Ø50d (1,288,305) gültig | KP3: MA50 aktuell 30.49 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Giant Base auf Wochenbasis, 30 Wochen von 2026-01-30 bis 2026-08-28; Cup-Tiefe 44 %, Rücksetzer 38 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.53; Ziel = Kaufpunkt plus Cup-Höhe | KP2: Box 34.39–40.83; Breakout nur mit Volumen über Ø50d (1,288,716) gültig | KP3: MA50 aktuell 30.49 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 13 Wochen von 2026-05-22 bis 2026-08-21; Cup-Tiefe 25 %, Rücksetzer 40 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.86; Ziel = Kaufpunkt plus Cup-Höhe | KP2: Box 32.75–35.50; Breakout nur mit Volumen über Ø50d (115,851) gültig | KP3: MA50 aktuell 30.38 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Giant Base auf Wochenbasis, 13 Wochen von 2026-05-22 bis 2026-08-21; Cup-Tiefe 25 %, Rücksetzer 40 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.86; Ziel = Kaufpunkt plus Cup-Höhe | KP2: Box 32.75–35.50; Breakout nur mit Volumen über Ø50d (115,850) gültig | KP3: MA50 aktuell 30.38 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 46.79–52.91; Breakout nur mit Volumen über Ø50d (1,142,953) gültig | KP2: MA50 aktuell 45.19 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 52.91</t>
+          <t>KP1: Box 46.79–52.91; Breakout nur mit Volumen über Ø50d (1,142,954) gültig | KP2: MA50 aktuell 45.19 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 52.91</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 25.78–30.24; Breakout nur mit Volumen über Ø50d (812,794) gültig | KP2: MA50 aktuell 23.18 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 30.24</t>
+          <t>KP1: Box 25.78–30.24; Breakout nur mit Volumen über Ø50d (813,900) gültig | KP2: MA50 aktuell 23.18 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 30.24</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 48.25–53.67; Breakout nur mit Volumen über Ø50d (1,154,465) gültig | KP2: MA50 aktuell 40.71 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 53.67</t>
+          <t>KP1: Box 48.25–53.67; Breakout nur mit Volumen über Ø50d (1,154,468) gültig | KP2: MA50 aktuell 40.71 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 53.67</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 105.05–117.88; Breakout nur mit Volumen über Ø50d (908,483) gültig | KP2: MA50 aktuell 105.24 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 117.88</t>
+          <t>KP1: Box 105.05–117.88; Breakout nur mit Volumen über Ø50d (908,484) gültig | KP2: MA50 aktuell 105.24 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 117.88</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 75.16–87.42; Breakout nur mit Volumen über Ø50d (191,381) gültig | KP2: MA50 aktuell 65.82 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 87.42</t>
+          <t>KP1: Box 75.16–87.42; Breakout nur mit Volumen über Ø50d (191,386) gültig | KP2: MA50 aktuell 65.82 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 87.42</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 157.11–176.58; Breakout nur mit Volumen über Ø50d (2,608,113) gültig | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 159.52 (nur bei intaktem Trend nutzen)</t>
+          <t>KP1: Box 157.11–176.58; Breakout nur mit Volumen über Ø50d (2,608,146) gültig | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 159.52 (nur bei intaktem Trend nutzen)</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 32.05–36.94; Breakout nur mit Volumen über Ø50d (2,116,768) gültig | KP2: MA50 aktuell 30.61 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 36.94</t>
+          <t>KP1: Box 32.05–36.94; Breakout nur mit Volumen über Ø50d (2,131,722) gültig | KP2: MA50 aktuell 30.61 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 36.94</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 16.55–18.89; Breakout nur mit Volumen über Ø50d (4,343,605) gültig | KP2: MA50 aktuell 14.53 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 18.89</t>
+          <t>KP1: Box 16.55–18.89; Breakout nur mit Volumen über Ø50d (4,343,606) gültig | KP2: MA50 aktuell 14.53 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 18.89</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 19.73–27.80; Breakout nur mit Volumen über Ø50d (1,542,626) gültig | KP2: MA50 aktuell 15.53 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 27.80</t>
+          <t>KP1: Box 19.73–27.80; Breakout nur mit Volumen über Ø50d (1,542,672) gültig | KP2: MA50 aktuell 15.53 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 27.80</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 151.80–173.89; Breakout nur mit Volumen über Ø50d (5,097,781) gültig | KP2: MA50 aktuell 158.78; Kauf erst wenn Schlusskurs drüber | KP3: 52W-Hoch 173.89 | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
+          <t>KP1: Box 151.80–173.89; Breakout nur mit Volumen über Ø50d (5,098,080) gültig | KP2: MA50 aktuell 158.78; Kauf erst wenn Schlusskurs drüber | KP3: 52W-Hoch 173.89 | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 206.82–231.81; Breakout nur mit Volumen über Ø50d (1,902,541) gültig | KP2: MA50 aktuell 198.18 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 231.81 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 206.82–231.81; Breakout nur mit Volumen über Ø50d (1,903,638) gültig | KP2: MA50 aktuell 198.18 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 231.81 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -8941,7 +8941,7 @@
         <v>104.5</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>105.43</v>
+        <v>105.5</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>42.26</v>
@@ -8975,18 +8975,18 @@
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>105.44</v>
+        <v>105.51</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>+1.0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="n">
-        <v>94.90000000000001</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="O73" s="2" t="n">
-        <v>123.05</v>
+        <v>123.12</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
@@ -9021,15 +9021,15 @@
         </is>
       </c>
       <c r="X73" s="2" t="n">
-        <v>105.54</v>
+        <v>105.61</v>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="Z73" s="2" t="n">
-        <v>98.05</v>
+        <v>98.12</v>
       </c>
       <c r="AA73" s="2" t="inlineStr"/>
       <c r="AB73" s="2" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 17 Wochen von 2026-05-08 bis 2026-09-04; Cup-Tiefe 19 %, Rücksetzer 44 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.88; Ziel = Kaufpunkt plus Cup-Höhe | KP2: MA50 aktuell 92.10 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 105.43 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Giant Base auf Wochenbasis, 17 Wochen von 2026-05-08 bis 2026-09-04; Cup-Tiefe 19 %, Rücksetzer 45 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.88; Ziel = Kaufpunkt plus Cup-Höhe | KP2: MA50 aktuell 92.10 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 105.50 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -9092,18 +9092,18 @@
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>45.1</v>
+        <v>45.13</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>+12.2%</t>
+          <t>+12.3%</t>
         </is>
       </c>
       <c r="N74" s="2" t="n">
-        <v>40.59</v>
+        <v>40.62</v>
       </c>
       <c r="O74" s="2" t="n">
-        <v>69.19</v>
+        <v>69.22</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
@@ -9489,11 +9489,11 @@
         </is>
       </c>
       <c r="X77" s="2" t="n">
-        <v>55.33</v>
+        <v>55.34</v>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>+0.3%</t>
         </is>
       </c>
       <c r="Z77" s="2" t="n">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 17.05–19.76; Breakout nur mit Volumen über Ø50d (2,535,530) gültig | KP2: MA50 aktuell 15.62 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 19.76 | TT fehlt: MA150 &gt; MA200</t>
+          <t>KP1: Box 17.05–19.76; Breakout nur mit Volumen über Ø50d (2,535,532) gültig | KP2: MA50 aktuell 15.62 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 19.76 | TT fehlt: MA150 &gt; MA200</t>
         </is>
       </c>
     </row>
@@ -10597,12 +10597,12 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>✗ +17%</t>
+          <t>✗ +13%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+2281%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -11033,44 +11033,44 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>SCCO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Southern Copper Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>198.76</v>
+        <v>112.09</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>221.67</v>
+        <v>199.3</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>96.29000000000001</v>
+        <v>77.05</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-43.8%</t>
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>✗ 7/8</t>
+          <t>✗ 4/8</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>✓ +41%</t>
+          <t>✓ +48%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>+72%</t>
+          <t>+8%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -11079,18 +11079,18 @@
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>199.96</v>
+        <v>114.91</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>+2.5%</t>
         </is>
       </c>
       <c r="N91" s="2" t="n">
-        <v>179.97</v>
+        <v>103.42</v>
       </c>
       <c r="O91" s="2" t="n">
-        <v>230.86</v>
+        <v>128.92</v>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
@@ -11103,15 +11103,15 @@
         </is>
       </c>
       <c r="R91" s="2" t="n">
-        <v>221.89</v>
+        <v>199.5</v>
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>+11.6%</t>
+          <t>+78.0%</t>
         </is>
       </c>
       <c r="T91" s="2" t="n">
-        <v>206.16</v>
+        <v>185.35</v>
       </c>
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
@@ -11121,176 +11121,176 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="X91" s="2" t="n">
-        <v>188.85</v>
+        <v>131.95</v>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>+17.7%</t>
         </is>
       </c>
       <c r="Z91" s="2" t="n">
-        <v>178.51</v>
+        <v>118.76</v>
       </c>
       <c r="AA91" s="2" t="inlineStr"/>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>KP1: Range 169.05–199.95; Berührungen oben 3, unten 3; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 221.67 | KP3: MA50 aktuell 187.91 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Range 100.89–114.90; Berührungen oben 2, unten 2; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 199.30 | KP3: Hoch der letzten 20 Handelstage | TT fehlt: MA150 &gt; MA200; MA200 steigt (≥1 Monat); ≤25 % unter 52W-Hoch</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>SM Energy Co</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>112.09</v>
+        <v>36.44</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>199.3</v>
+        <v>38.94</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>77.05</v>
+        <v>17.45</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>-43.8%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>✗ 4/8</t>
+          <t>✗ 7/8</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>✓ +48%</t>
+          <t>✓ +176%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>+8%</t>
+          <t>+154%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Rectangle Top</t>
+          <t>Cup &amp; Handle (Wochenbasis)</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>114.91</v>
+        <v>38.95</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>+6.9%</t>
         </is>
       </c>
       <c r="N92" s="2" t="n">
-        <v>103.42</v>
+        <v>35.06</v>
       </c>
       <c r="O92" s="2" t="n">
-        <v>128.92</v>
+        <v>49.36</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>Range steht — SMA21-Filter noch NICHT erfüllt</t>
+          <t>Score 84/100</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>Fallback: 52W-Hoch-Breakout</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="R92" s="2" t="n">
-        <v>199.5</v>
+        <v>32.24</v>
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>+78.0%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T92" s="2" t="n">
-        <v>185.35</v>
+        <v>30.47</v>
       </c>
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — generischer Breakout-Level</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: 52W-Hoch-Breakout</t>
         </is>
       </c>
       <c r="X92" s="2" t="n">
-        <v>131.95</v>
+        <v>38.98</v>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>+17.7%</t>
+          <t>+7.0%</t>
         </is>
       </c>
       <c r="Z92" s="2" t="n">
-        <v>118.76</v>
+        <v>36.21</v>
       </c>
       <c r="AA92" s="2" t="inlineStr"/>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kein Muster — generischer Breakout-Level</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>KP1: Range 100.89–114.90; Berührungen oben 2, unten 2; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 199.30 | KP3: Hoch der letzten 20 Handelstage | TT fehlt: MA150 &gt; MA200; MA200 steigt (≥1 Monat); ≤25 % unter 52W-Hoch</t>
+          <t>KP1: Giant Base auf Wochenbasis, 15 Wochen von 2026-05-22 bis 2026-09-04; Cup-Tiefe 29 %, Rücksetzer 26 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.84; Ziel = Kaufpunkt plus Cup-Höhe | KP2: MA50 aktuell 32.08 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 38.94 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>SN</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SM Energy Co</t>
+          <t>SharkNinja Inc</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>36.44</v>
+        <v>173.38</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>38.94</v>
+        <v>194.54</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>17.45</v>
+        <v>83.12</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -11299,12 +11299,12 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>✓ +176%</t>
+          <t>✗ +22%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>+154%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -11313,139 +11313,139 @@
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>38.95</v>
+        <v>164.38</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>+6.9%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="N93" s="2" t="n">
-        <v>35.06</v>
+        <v>147.95</v>
       </c>
       <c r="O93" s="2" t="n">
-        <v>49.36</v>
+        <v>201.51</v>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>Score 84/100</t>
+          <t>Score 71/100</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 52W-Hoch-Breakout</t>
         </is>
       </c>
       <c r="R93" s="2" t="n">
-        <v>32.24</v>
+        <v>194.73</v>
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>+12.3%</t>
         </is>
       </c>
       <c r="T93" s="2" t="n">
-        <v>30.47</v>
+        <v>180.92</v>
       </c>
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — generischer Breakout-Level</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>Fallback: 52W-Hoch-Breakout</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="X93" s="2" t="n">
-        <v>38.98</v>
+        <v>167.67</v>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>+7.0%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="Z93" s="2" t="n">
-        <v>36.21</v>
+        <v>158.5</v>
       </c>
       <c r="AA93" s="2" t="inlineStr"/>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — generischer Breakout-Level</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 15 Wochen von 2026-05-22 bis 2026-09-04; Cup-Tiefe 29 %, Rücksetzer 26 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.84; Ziel = Kaufpunkt plus Cup-Höhe | KP2: MA50 aktuell 32.08 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 38.94 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Giant Base auf Wochenbasis, 23 Wochen von 2026-02-20 bis 2026-07-31; Cup-Tiefe 28 %, Rücksetzer 36 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.87; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 194.54 | KP3: MA50 aktuell 166.84 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>SOLS</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>SharkNinja Inc</t>
+          <t>Solstice Advanced Materials Inc</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>173.38</v>
+        <v>63.73</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>194.54</v>
+        <v>90.8</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>83.12</v>
+        <v>40.43</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-29.8%</t>
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>✗ 7/8</t>
+          <t>✗ 3/8</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>✗ +22%</t>
+          <t>✗ +11%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>+23%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Cup &amp; Handle (Wochenbasis)</t>
+          <t>Rectangle Top</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>164.38</v>
+        <v>66.36</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>+4.1%</t>
         </is>
       </c>
       <c r="N94" s="2" t="n">
-        <v>147.95</v>
+        <v>59.73</v>
       </c>
       <c r="O94" s="2" t="n">
-        <v>201.51</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>Score 71/100</t>
+          <t>Setup komplett (Kurs &gt; SMA21)</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11454,15 +11454,15 @@
         </is>
       </c>
       <c r="R94" s="2" t="n">
-        <v>194.73</v>
+        <v>90.89</v>
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>+12.3%</t>
+          <t>+42.6%</t>
         </is>
       </c>
       <c r="T94" s="2" t="n">
-        <v>180.92</v>
+        <v>84.44</v>
       </c>
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
@@ -11472,97 +11472,97 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="X94" s="2" t="n">
-        <v>167.67</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>+5.9%</t>
         </is>
       </c>
       <c r="Z94" s="2" t="n">
-        <v>158.5</v>
+        <v>60.76</v>
       </c>
       <c r="AA94" s="2" t="inlineStr"/>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 23 Wochen von 2026-02-20 bis 2026-07-31; Cup-Tiefe 28 %, Rücksetzer 36 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.87; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 194.54 | KP3: MA50 aktuell 166.84 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Range 59.47–66.35; Berührungen oben 2, unten 3; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 90.80 | KP3: Hoch der letzten 20 Handelstage | TT fehlt: Kurs &gt; MA150 &amp; MA200; MA200 steigt (≥1 Monat); MA50 &gt; MA150 &amp; MA200</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SOLS</t>
+          <t>SRPT</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Solstice Advanced Materials Inc</t>
+          <t>Sarepta Therapeutics Inc</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>63.73</v>
+        <v>22.5</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>90.8</v>
+        <v>25.32</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>40.43</v>
+        <v>14.68</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>✗ 3/8</t>
+          <t>✗ 4/8</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>✗ +11%</t>
+          <t>✗ -34%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>+23%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Rectangle Top</t>
+          <t>Cup &amp; Handle (Wochenbasis)</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>66.36</v>
+        <v>23.63</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>+5.0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="n">
-        <v>59.73</v>
+        <v>21.27</v>
       </c>
       <c r="O95" s="2" t="n">
-        <v>73.23999999999999</v>
+        <v>32.8</v>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>Setup komplett (Kurs &gt; SMA21)</t>
+          <t>Score 72/100</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11571,15 +11571,15 @@
         </is>
       </c>
       <c r="R95" s="2" t="n">
-        <v>90.89</v>
+        <v>25.35</v>
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>+42.6%</t>
+          <t>+12.7%</t>
         </is>
       </c>
       <c r="T95" s="2" t="n">
-        <v>84.44</v>
+        <v>23.55</v>
       </c>
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
@@ -11589,73 +11589,73 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="X95" s="2" t="n">
-        <v>67.51000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>+5.9%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="Z95" s="2" t="n">
-        <v>60.76</v>
+        <v>17.3</v>
       </c>
       <c r="AA95" s="2" t="inlineStr"/>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>KP1: Range 59.47–66.35; Berührungen oben 2, unten 3; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 90.80 | KP3: Hoch der letzten 20 Handelstage | TT fehlt: Kurs &gt; MA150 &amp; MA200; MA200 steigt (≥1 Monat); MA50 &gt; MA150 &amp; MA200</t>
+          <t>KP1: Giant Base auf Wochenbasis, 23 Wochen von 2026-03-27 bis 2026-09-04; Cup-Tiefe 38 %, Rücksetzer 38 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.63; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 25.32 | KP3: MA50 aktuell 18.21 (nur bei intaktem Trend nutzen) | TT fehlt: MA150 &gt; MA200; MA200 steigt (≥1 Monat); MA50 &gt; MA150 &amp; MA200</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SRPT</t>
+          <t>SSRM</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Sarepta Therapeutics Inc</t>
+          <t>SSR Mining Inc</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>22.5</v>
+        <v>37.15</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>25.32</v>
+        <v>39.44</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>14.68</v>
+        <v>18.19</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>✗ 4/8</t>
+          <t>✗ 7/8</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>✗ -34%</t>
+          <t>✗ +10%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+11%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -11664,101 +11664,101 @@
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>23.63</v>
+        <v>39.45</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>+5.0%</t>
+          <t>+6.2%</t>
         </is>
       </c>
       <c r="N96" s="2" t="n">
-        <v>21.27</v>
+        <v>35.51</v>
       </c>
       <c r="O96" s="2" t="n">
-        <v>32.8</v>
+        <v>49.12</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>Score 72/100</t>
+          <t>Score 81/100</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>Fallback: 52W-Hoch-Breakout</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="R96" s="2" t="n">
-        <v>25.35</v>
+        <v>31.09</v>
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>+12.7%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="T96" s="2" t="n">
-        <v>23.55</v>
+        <v>29.39</v>
       </c>
       <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — generischer Breakout-Level</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 52W-Hoch-Breakout</t>
         </is>
       </c>
       <c r="X96" s="2" t="n">
-        <v>18.3</v>
+        <v>39.48</v>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>+6.3%</t>
         </is>
       </c>
       <c r="Z96" s="2" t="n">
-        <v>17.3</v>
+        <v>36.68</v>
       </c>
       <c r="AA96" s="2" t="inlineStr"/>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — generischer Breakout-Level</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 23 Wochen von 2026-03-27 bis 2026-09-04; Cup-Tiefe 38 %, Rücksetzer 38 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.63; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 25.32 | KP3: MA50 aktuell 18.21 (nur bei intaktem Trend nutzen) | TT fehlt: MA150 &gt; MA200; MA200 steigt (≥1 Monat); MA50 &gt; MA150 &amp; MA200</t>
+          <t>KP1: Giant Base auf Wochenbasis, 11 Wochen von 2026-06-19 bis 2026-09-04; Cup-Tiefe 29 %, Rücksetzer 39 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.90; Ziel = Kaufpunkt plus Cup-Höhe | KP2: MA50 aktuell 30.93 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 39.44 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>SSRM</t>
+          <t>SU</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>SSR Mining Inc</t>
+          <t>Suncor Energy Inc</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>37.15</v>
+        <v>67.33</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>39.44</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>18.19</v>
+        <v>37.77</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -11767,12 +11767,12 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>✗ +10%</t>
+          <t>✓ +46%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>+11%</t>
+          <t>+242%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -11781,115 +11781,115 @@
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>39.45</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>+6.2%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="N97" s="2" t="n">
-        <v>35.51</v>
+        <v>62.24</v>
       </c>
       <c r="O97" s="2" t="n">
-        <v>49.12</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>Score 81/100</t>
+          <t>Score 75/100</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 52W-Hoch-Breakout</t>
         </is>
       </c>
       <c r="R97" s="2" t="n">
-        <v>31.09</v>
+        <v>70.36</v>
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>+4.5%</t>
         </is>
       </c>
       <c r="T97" s="2" t="n">
-        <v>29.39</v>
+        <v>65.37</v>
       </c>
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — generischer Breakout-Level</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>Fallback: 52W-Hoch-Breakout</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="X97" s="2" t="n">
-        <v>39.48</v>
+        <v>63.5</v>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>+6.3%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Z97" s="2" t="n">
-        <v>36.68</v>
+        <v>60.02</v>
       </c>
       <c r="AA97" s="2" t="inlineStr"/>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — generischer Breakout-Level</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 11 Wochen von 2026-06-19 bis 2026-09-04; Cup-Tiefe 29 %, Rücksetzer 39 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.90; Ziel = Kaufpunkt plus Cup-Höhe | KP2: MA50 aktuell 30.93 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 39.44 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Giant Base auf Wochenbasis, 15 Wochen von 2026-05-08 bis 2026-08-21; Cup-Tiefe 24 %, Rücksetzer 27 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.59; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 70.29 | KP3: MA50 aktuell 63.18 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>SU</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Suncor Energy Inc</t>
+          <t>Veeva Systems Inc</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>67.33</v>
+        <v>275.09</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>70.29000000000001</v>
+        <v>310.5</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>37.77</v>
+        <v>148.05</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>✗ 7/8</t>
+          <t>✗ 5/8</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>✓ +46%</t>
+          <t>✗ +18%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>+242%</t>
+          <t>+40%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -11898,22 +11898,22 @@
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>69.15000000000001</v>
+        <v>296.25</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>+2.7%</t>
+          <t>+7.7%</t>
         </is>
       </c>
       <c r="N98" s="2" t="n">
-        <v>62.24</v>
+        <v>266.63</v>
       </c>
       <c r="O98" s="2" t="n">
-        <v>86.15000000000001</v>
+        <v>450.37</v>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>Score 75/100</t>
+          <t>Score 83/100</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11922,15 +11922,15 @@
         </is>
       </c>
       <c r="R98" s="2" t="n">
-        <v>70.36</v>
+        <v>310.81</v>
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>+4.5%</t>
+          <t>+13.0%</t>
         </is>
       </c>
       <c r="T98" s="2" t="n">
-        <v>65.37</v>
+        <v>288.77</v>
       </c>
       <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" s="2" t="inlineStr">
@@ -11944,15 +11944,15 @@
         </is>
       </c>
       <c r="X98" s="2" t="n">
-        <v>63.5</v>
+        <v>221.1</v>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="Z98" s="2" t="n">
-        <v>60.02</v>
+        <v>209</v>
       </c>
       <c r="AA98" s="2" t="inlineStr"/>
       <c r="AB98" s="2" t="inlineStr">
@@ -11962,37 +11962,37 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 15 Wochen von 2026-05-08 bis 2026-08-21; Cup-Tiefe 24 %, Rücksetzer 27 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.59; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 70.29 | KP3: MA50 aktuell 63.18 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Giant Base auf Wochenbasis, 41 Wochen von 2025-11-14 bis 2026-08-28; Cup-Tiefe 51 %, Rücksetzer 37 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.87; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 310.50 | KP3: MA50 aktuell 220.00 (nur bei intaktem Trend nutzen) | TT fehlt: MA150 &gt; MA200; MA200 steigt (≥1 Monat); RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>VNOM</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Veeva Systems Inc</t>
+          <t>Viper Energy Inc</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>275.09</v>
+        <v>44.39</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>310.5</v>
+        <v>51.13</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>148.05</v>
+        <v>35.1</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -12001,36 +12001,36 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>✗ +18%</t>
+          <t>✓ +115%</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>+40%</t>
+          <t>+161%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>Cup &amp; Handle (Wochenbasis)</t>
+          <t>Rectangle Top</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>296.25</v>
+        <v>45.44</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>+7.7%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="N99" s="2" t="n">
-        <v>266.63</v>
+        <v>42.02</v>
       </c>
       <c r="O99" s="2" t="n">
-        <v>450.37</v>
+        <v>48.84</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>Score 83/100</t>
+          <t>Setup komplett (Kurs &gt; SMA21)</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12039,15 +12039,15 @@
         </is>
       </c>
       <c r="R99" s="2" t="n">
-        <v>310.81</v>
+        <v>51.18</v>
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>+13.0%</t>
+          <t>+15.3%</t>
         </is>
       </c>
       <c r="T99" s="2" t="n">
-        <v>288.77</v>
+        <v>47.55</v>
       </c>
       <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" s="2" t="inlineStr">
@@ -12061,15 +12061,15 @@
         </is>
       </c>
       <c r="X99" s="2" t="n">
-        <v>221.1</v>
+        <v>43.52</v>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="Z99" s="2" t="n">
-        <v>209</v>
+        <v>41.14</v>
       </c>
       <c r="AA99" s="2" t="inlineStr"/>
       <c r="AB99" s="2" t="inlineStr">
@@ -12079,154 +12079,154 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 41 Wochen von 2025-11-14 bis 2026-08-28; Cup-Tiefe 51 %, Rücksetzer 37 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.87; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 310.50 | KP3: MA50 aktuell 220.00 (nur bei intaktem Trend nutzen) | TT fehlt: MA150 &gt; MA200; MA200 steigt (≥1 Monat); RS-Rank ≥ 70</t>
+          <t>KP1: Range 42.03–45.43; Berührungen oben 4, unten 2; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 51.13 | KP3: MA50 aktuell 43.30 (nur bei intaktem Trend nutzen) | TT fehlt: Kurs &gt; MA150 &amp; MA200; MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>VNOM</t>
+          <t>WES</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Viper Energy Inc</t>
+          <t>Western Midstream Partners LP</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>44.39</v>
+        <v>49.54</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>51.13</v>
+        <v>50.07</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>35.1</v>
+        <v>36.9</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>✗ 5/8</t>
+          <t>✗ 7/8</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>✓ +115%</t>
+          <t>✓ +30%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>+161%</t>
+          <t>+14%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>Rectangle Top</t>
+          <t>Cup &amp; Handle (Wochenbasis)</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>45.44</v>
+        <v>50.08</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="N100" s="2" t="n">
-        <v>42.02</v>
+        <v>45.08</v>
       </c>
       <c r="O100" s="2" t="n">
-        <v>48.84</v>
+        <v>55.98</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>Setup komplett (Kurs &gt; SMA21)</t>
+          <t>Score 77/100</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>Fallback: 52W-Hoch-Breakout</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="R100" s="2" t="n">
-        <v>51.18</v>
+        <v>47.12</v>
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>+15.3%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T100" s="2" t="n">
-        <v>47.55</v>
+        <v>44.54</v>
       </c>
       <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — generischer Breakout-Level</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 52W-Hoch-Breakout</t>
         </is>
       </c>
       <c r="X100" s="2" t="n">
-        <v>43.52</v>
+        <v>50.12</v>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="Z100" s="2" t="n">
-        <v>41.14</v>
+        <v>46.57</v>
       </c>
       <c r="AA100" s="2" t="inlineStr"/>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — generischer Breakout-Level</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>KP1: Range 42.03–45.43; Berührungen oben 4, unten 2; Ziel = Ausbruch + Rechteckhöhe | KP2: 52W-Hoch 51.13 | KP3: MA50 aktuell 43.30 (nur bei intaktem Trend nutzen) | TT fehlt: Kurs &gt; MA150 &amp; MA200; MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
+          <t>KP1: Giant Base auf Wochenbasis, 13 Wochen von 2026-05-22 bis 2026-08-21; Cup-Tiefe 12 %, Rücksetzer 42 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.91; Ziel = Kaufpunkt plus Cup-Höhe | KP2: MA50 aktuell 46.88 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 50.07 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>WES</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Western Midstream Partners LP</t>
+          <t>Cactus Inc</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>49.54</v>
+        <v>70.16</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>50.07</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>36.9</v>
+        <v>33.2</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -12235,12 +12235,12 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>✓ +30%</t>
+          <t>✓ +64%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>+14%</t>
+          <t>+19%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -12249,22 +12249,22 @@
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>50.08</v>
+        <v>74.08</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>+5.6%</t>
         </is>
       </c>
       <c r="N101" s="2" t="n">
-        <v>45.08</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="O101" s="2" t="n">
-        <v>55.98</v>
+        <v>110.89</v>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>Score 77/100</t>
+          <t>Score 81/100</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12273,15 +12273,15 @@
         </is>
       </c>
       <c r="R101" s="2" t="n">
-        <v>47.12</v>
+        <v>62.16</v>
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T101" s="2" t="n">
-        <v>44.54</v>
+        <v>58.76</v>
       </c>
       <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" s="2" t="inlineStr">
@@ -12295,15 +12295,15 @@
         </is>
       </c>
       <c r="X101" s="2" t="n">
-        <v>50.12</v>
+        <v>74.14</v>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+5.7%</t>
         </is>
       </c>
       <c r="Z101" s="2" t="n">
-        <v>46.57</v>
+        <v>68.89</v>
       </c>
       <c r="AA101" s="2" t="inlineStr"/>
       <c r="AB101" s="2" t="inlineStr">
@@ -12313,51 +12313,51 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 13 Wochen von 2026-05-22 bis 2026-08-21; Cup-Tiefe 12 %, Rücksetzer 42 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.91; Ziel = Kaufpunkt plus Cup-Höhe | KP2: MA50 aktuell 46.88 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 50.07 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Giant Base auf Wochenbasis, 92 Wochen von 2024-11-15 bis 2026-08-21; Cup-Tiefe 53 %, Rücksetzer 23 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.68; Ziel = Kaufpunkt plus Cup-Höhe | KP2: MA50 aktuell 61.85 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 74.07 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Cactus Inc</t>
+          <t>Wheaton Precious Metals Corp</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>70.16</v>
+        <v>154.98</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>74.06999999999999</v>
+        <v>165.76</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>33.2</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>✗ 7/8</t>
+          <t>✗ 6/8</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>✓ +64%</t>
+          <t>✓ +85%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>+19%</t>
+          <t>+86%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -12366,115 +12366,115 @@
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>74.08</v>
+        <v>163.91</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>+5.8%</t>
         </is>
       </c>
       <c r="N102" s="2" t="n">
-        <v>66.68000000000001</v>
+        <v>147.52</v>
       </c>
       <c r="O102" s="2" t="n">
-        <v>110.89</v>
+        <v>216.49</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>Score 81/100</t>
+          <t>Score 71/100</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 52W-Hoch-Breakout</t>
         </is>
       </c>
       <c r="R102" s="2" t="n">
-        <v>62.16</v>
+        <v>165.93</v>
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>+7.1%</t>
         </is>
       </c>
       <c r="T102" s="2" t="n">
-        <v>58.76</v>
+        <v>154.16</v>
       </c>
       <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — generischer Breakout-Level</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>Fallback: 52W-Hoch-Breakout</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="X102" s="2" t="n">
-        <v>74.14</v>
+        <v>126.73</v>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>+5.7%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z102" s="2" t="n">
-        <v>68.89</v>
+        <v>119.79</v>
       </c>
       <c r="AA102" s="2" t="inlineStr"/>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — generischer Breakout-Level</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 92 Wochen von 2024-11-15 bis 2026-08-21; Cup-Tiefe 53 %, Rücksetzer 23 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.68; Ziel = Kaufpunkt plus Cup-Höhe | KP2: MA50 aktuell 61.85 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 74.07 | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Giant Base auf Wochenbasis, 19 Wochen von 2026-04-17 bis 2026-08-28; Cup-Tiefe 34 %, Rücksetzer 38 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.75; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 165.76 | KP3: MA50 aktuell 126.10 (nur bei intaktem Trend nutzen) | TT fehlt: MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>WTTR</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Wheaton Precious Metals Corp</t>
+          <t>Select Water Solutions Inc</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>154.98</v>
+        <v>20.06</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>165.76</v>
+        <v>22.55</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>92.56999999999999</v>
+        <v>8.23</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>✗ 6/8</t>
+          <t>✗ 7/8</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>✓ +85%</t>
+          <t>✗ +9%</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>+86%</t>
+          <t>+62%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -12483,22 +12483,22 @@
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>163.91</v>
+        <v>20.49</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>+5.8%</t>
+          <t>+2.1%</t>
         </is>
       </c>
       <c r="N103" s="2" t="n">
-        <v>147.52</v>
+        <v>18.45</v>
       </c>
       <c r="O103" s="2" t="n">
-        <v>216.49</v>
+        <v>28.43</v>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>Score 71/100</t>
+          <t>Score 74/100</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12507,15 +12507,15 @@
         </is>
       </c>
       <c r="R103" s="2" t="n">
-        <v>165.93</v>
+        <v>22.57</v>
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>+7.1%</t>
+          <t>+12.5%</t>
         </is>
       </c>
       <c r="T103" s="2" t="n">
-        <v>154.16</v>
+        <v>20.97</v>
       </c>
       <c r="U103" s="2" t="inlineStr"/>
       <c r="V103" s="2" t="inlineStr">
@@ -12525,59 +12525,59 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="X103" s="2" t="n">
-        <v>126.73</v>
+        <v>21.84</v>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>+8.9%</t>
         </is>
       </c>
       <c r="Z103" s="2" t="n">
-        <v>119.79</v>
+        <v>19.66</v>
       </c>
       <c r="AA103" s="2" t="inlineStr"/>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 19 Wochen von 2026-04-17 bis 2026-08-28; Cup-Tiefe 34 %, Rücksetzer 38 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.75; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 165.76 | KP3: MA50 aktuell 126.10 (nur bei intaktem Trend nutzen) | TT fehlt: MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
+          <t>KP1: Giant Base auf Wochenbasis, 76 Wochen von 2024-12-06 bis 2026-05-22; Cup-Tiefe 52 %, Rücksetzer 40 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.91; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 22.55 | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>WTTR</t>
+          <t>XNCR</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Select Water Solutions Inc</t>
+          <t>Xencor Inc</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>20.06</v>
+        <v>26.61</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>22.55</v>
+        <v>30.61</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>8.23</v>
+        <v>8.19</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -12586,115 +12586,113 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>✗ +9%</t>
+          <t>✗ +18%</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>+62%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>Cup &amp; Handle (Wochenbasis)</t>
+          <t>Darvas Box</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>20.49</v>
+        <v>30.62</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+15.1%</t>
         </is>
       </c>
       <c r="N104" s="2" t="n">
-        <v>18.45</v>
-      </c>
-      <c r="O104" s="2" t="n">
-        <v>28.43</v>
-      </c>
+        <v>27.56</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr"/>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>Score 74/100</t>
+          <t>Box bestätigt — auf Breakout mit Volumen warten</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>Fallback: 52W-Hoch-Breakout</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="R104" s="2" t="n">
-        <v>22.57</v>
+        <v>21.17</v>
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>+12.5%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="T104" s="2" t="n">
-        <v>20.97</v>
+        <v>20.01</v>
       </c>
       <c r="U104" s="2" t="inlineStr"/>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — generischer Breakout-Level</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: 52W-Hoch-Breakout</t>
         </is>
       </c>
       <c r="X104" s="2" t="n">
-        <v>21.84</v>
+        <v>30.64</v>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>+8.9%</t>
+          <t>+15.1%</t>
         </is>
       </c>
       <c r="Z104" s="2" t="n">
-        <v>19.66</v>
+        <v>28.47</v>
       </c>
       <c r="AA104" s="2" t="inlineStr"/>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kein Muster — generischer Breakout-Level</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>KP1: Giant Base auf Wochenbasis, 76 Wochen von 2024-12-06 bis 2026-05-22; Cup-Tiefe 52 %, Rücksetzer 40 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.91; Ziel = Kaufpunkt plus Cup-Höhe | KP2: 52W-Hoch 22.55 | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: Box 25.81–30.61; Breakout nur mit Volumen über Ø50d (1,206,400) gültig | KP2: MA50 aktuell 21.06 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 30.61 | TT fehlt: MA150 &gt; MA200</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>XNCR</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Xencor Inc</t>
+          <t>Zeta Global Holdings Corp</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>26.61</v>
+        <v>31.35</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>30.61</v>
+        <v>32.81</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>8.19</v>
+        <v>14.36</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -12703,7 +12701,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>✗ +18%</t>
+          <t>✓ +44%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -12713,24 +12711,26 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>Darvas Box</t>
+          <t>Cup &amp; Handle (Wochenbasis)</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>30.62</v>
+        <v>32.82</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>+15.1%</t>
+          <t>+4.7%</t>
         </is>
       </c>
       <c r="N105" s="2" t="n">
-        <v>27.56</v>
-      </c>
-      <c r="O105" s="2" t="inlineStr"/>
+        <v>29.54</v>
+      </c>
+      <c r="O105" s="2" t="n">
+        <v>43.35</v>
+      </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>Box bestätigt — auf Breakout mit Volumen warten</t>
+          <t>Score 80/100</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12739,15 +12739,15 @@
         </is>
       </c>
       <c r="R105" s="2" t="n">
-        <v>21.17</v>
+        <v>24.98</v>
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="T105" s="2" t="n">
-        <v>20.01</v>
+        <v>23.61</v>
       </c>
       <c r="U105" s="2" t="inlineStr"/>
       <c r="V105" s="2" t="inlineStr">
@@ -12761,15 +12761,15 @@
         </is>
       </c>
       <c r="X105" s="2" t="n">
-        <v>30.64</v>
+        <v>32.84</v>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>+15.1%</t>
+          <t>+4.8%</t>
         </is>
       </c>
       <c r="Z105" s="2" t="n">
-        <v>28.47</v>
+        <v>30.51</v>
       </c>
       <c r="AA105" s="2" t="inlineStr"/>
       <c r="AB105" s="2" t="inlineStr">
@@ -12779,154 +12779,152 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>KP1: Box 25.81–30.61; Breakout nur mit Volumen über Ø50d (1,206,396) gültig | KP2: MA50 aktuell 21.06 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 30.61 | TT fehlt: MA150 &gt; MA200</t>
+          <t>KP1: Giant Base auf Wochenbasis, 34 Wochen von 2026-01-09 bis 2026-09-04; Cup-Tiefe 42 %, Rücksetzer 29 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.88; Ziel = Kaufpunkt plus Cup-Höhe | KP2: MA50 aktuell 24.85 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 32.81 | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>ZETA</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Zeta Global Holdings Corp</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="n">
-        <v>31.35</v>
-      </c>
-      <c r="D106" s="2" t="n">
-        <v>32.81</v>
-      </c>
-      <c r="E106" s="2" t="n">
-        <v>14.36</v>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>-4.4%</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>✗ 7/8</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>✓ +44%</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>Cup &amp; Handle (Wochenbasis)</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>32.82</v>
-      </c>
-      <c r="M106" s="2" t="inlineStr">
-        <is>
-          <t>+4.7%</t>
-        </is>
-      </c>
-      <c r="N106" s="2" t="n">
-        <v>29.54</v>
-      </c>
-      <c r="O106" s="2" t="n">
-        <v>43.35</v>
-      </c>
-      <c r="P106" s="2" t="inlineStr">
-        <is>
-          <t>Score 80/100</t>
-        </is>
-      </c>
-      <c r="Q106" s="2" t="inlineStr">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>ATI</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>ATI Inc</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>210.65</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>243.57</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>74.45</v>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>-13.5%</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>✓ 8/8</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>✗ +11%</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>+56%</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>Fallback: 52W-Hoch-Breakout</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="n">
+        <v>243.81</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>+15.7%</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="n">
+        <v>226.52</v>
+      </c>
+      <c r="O106" s="3" t="inlineStr"/>
+      <c r="P106" s="3" t="inlineStr">
+        <is>
+          <t>Kein Muster — generischer Breakout-Level</t>
+        </is>
+      </c>
+      <c r="Q106" s="3" t="inlineStr">
         <is>
           <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
-      <c r="R106" s="2" t="n">
-        <v>24.98</v>
-      </c>
-      <c r="S106" s="2" t="inlineStr">
-        <is>
-          <t>-20.3%</t>
-        </is>
-      </c>
-      <c r="T106" s="2" t="n">
-        <v>23.61</v>
-      </c>
-      <c r="U106" s="2" t="inlineStr"/>
-      <c r="V106" s="2" t="inlineStr">
+      <c r="R106" s="3" t="n">
+        <v>203.42</v>
+      </c>
+      <c r="S106" s="3" t="inlineStr">
+        <is>
+          <t>-3.4%</t>
+        </is>
+      </c>
+      <c r="T106" s="3" t="n">
+        <v>192.29</v>
+      </c>
+      <c r="U106" s="3" t="inlineStr"/>
+      <c r="V106" s="3" t="inlineStr">
         <is>
           <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
-      <c r="W106" s="2" t="inlineStr">
-        <is>
-          <t>Fallback: 52W-Hoch-Breakout</t>
-        </is>
-      </c>
-      <c r="X106" s="2" t="n">
-        <v>32.84</v>
-      </c>
-      <c r="Y106" s="2" t="inlineStr">
-        <is>
-          <t>+4.8%</t>
-        </is>
-      </c>
-      <c r="Z106" s="2" t="n">
-        <v>30.51</v>
-      </c>
-      <c r="AA106" s="2" t="inlineStr"/>
-      <c r="AB106" s="2" t="inlineStr">
-        <is>
-          <t>Kein Muster — generischer Breakout-Level</t>
-        </is>
-      </c>
-      <c r="AC106" s="2" t="inlineStr">
-        <is>
-          <t>KP1: Giant Base auf Wochenbasis, 34 Wochen von 2026-01-09 bis 2026-09-04; Cup-Tiefe 42 %, Rücksetzer 29 % der Cup-Höhe; U-Form bestätigt, Bestimmtheitsmaß 0.88; Ziel = Kaufpunkt plus Cup-Höhe | KP2: MA50 aktuell 24.85 (nur bei intaktem Trend nutzen) | KP3: 52W-Hoch 32.81 | TT fehlt: RS-Rank ≥ 70</t>
+      <c r="W106" s="3" t="inlineStr">
+        <is>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+        </is>
+      </c>
+      <c r="X106" s="3" t="n">
+        <v>243.58</v>
+      </c>
+      <c r="Y106" s="3" t="inlineStr">
+        <is>
+          <t>+15.6%</t>
+        </is>
+      </c>
+      <c r="Z106" s="3" t="n">
+        <v>219.23</v>
+      </c>
+      <c r="AA106" s="3" t="inlineStr"/>
+      <c r="AB106" s="3" t="inlineStr">
+        <is>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
+        </is>
+      </c>
+      <c r="AC106" s="3" t="inlineStr">
+        <is>
+          <t>KP1: 52W-Hoch 243.57 | KP2: MA50 aktuell 202.41 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>ATI</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>ATI Inc</t>
+          <t>Calumet Inc</t>
         </is>
       </c>
       <c r="C107" s="3" t="n">
-        <v>210.65</v>
+        <v>53.13</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>243.57</v>
+        <v>54.7</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>74.45</v>
+        <v>16.75</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="G107" s="3" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
@@ -12935,12 +12933,12 @@
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>✗ +11%</t>
+          <t>✓ +41%</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>+56%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K107" s="3" t="inlineStr">
@@ -12949,15 +12947,15 @@
         </is>
       </c>
       <c r="L107" s="3" t="n">
-        <v>243.81</v>
+        <v>54.75</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>+15.7%</t>
+          <t>+3.0%</t>
         </is>
       </c>
       <c r="N107" s="3" t="n">
-        <v>226.52</v>
+        <v>50.87</v>
       </c>
       <c r="O107" s="3" t="inlineStr"/>
       <c r="P107" s="3" t="inlineStr">
@@ -12971,15 +12969,15 @@
         </is>
       </c>
       <c r="R107" s="3" t="n">
-        <v>203.42</v>
+        <v>43.95</v>
       </c>
       <c r="S107" s="3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="T107" s="3" t="n">
-        <v>192.29</v>
+        <v>41.54</v>
       </c>
       <c r="U107" s="3" t="inlineStr"/>
       <c r="V107" s="3" t="inlineStr">
@@ -12993,15 +12991,15 @@
         </is>
       </c>
       <c r="X107" s="3" t="n">
-        <v>243.58</v>
+        <v>54.71</v>
       </c>
       <c r="Y107" s="3" t="inlineStr">
         <is>
-          <t>+15.6%</t>
+          <t>+3.0%</t>
         </is>
       </c>
       <c r="Z107" s="3" t="n">
-        <v>219.23</v>
+        <v>49.24</v>
       </c>
       <c r="AA107" s="3" t="inlineStr"/>
       <c r="AB107" s="3" t="inlineStr">
@@ -13011,37 +13009,37 @@
       </c>
       <c r="AC107" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 243.57 | KP2: MA50 aktuell 202.41 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
+          <t>KP1: 52W-Hoch 54.70 | KP2: MA50 aktuell 43.73 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>CORT</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Calumet Inc</t>
+          <t>Corcept Therapeutics Inc</t>
         </is>
       </c>
       <c r="C108" s="3" t="n">
-        <v>53.13</v>
+        <v>111.62</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>54.7</v>
+        <v>126.38</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>16.75</v>
+        <v>28.66</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="G108" s="3" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
@@ -13050,12 +13048,12 @@
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>✓ +41%</t>
+          <t>✓ +32%</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+24%</t>
         </is>
       </c>
       <c r="K108" s="3" t="inlineStr">
@@ -13064,15 +13062,15 @@
         </is>
       </c>
       <c r="L108" s="3" t="n">
-        <v>54.75</v>
+        <v>126.51</v>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>+3.0%</t>
+          <t>+13.3%</t>
         </is>
       </c>
       <c r="N108" s="3" t="n">
-        <v>50.87</v>
+        <v>117.53</v>
       </c>
       <c r="O108" s="3" t="inlineStr"/>
       <c r="P108" s="3" t="inlineStr">
@@ -13086,15 +13084,15 @@
         </is>
       </c>
       <c r="R108" s="3" t="n">
-        <v>43.95</v>
+        <v>104.6</v>
       </c>
       <c r="S108" s="3" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="T108" s="3" t="n">
-        <v>41.54</v>
+        <v>98.87</v>
       </c>
       <c r="U108" s="3" t="inlineStr"/>
       <c r="V108" s="3" t="inlineStr">
@@ -13108,15 +13106,15 @@
         </is>
       </c>
       <c r="X108" s="3" t="n">
-        <v>54.71</v>
+        <v>126.39</v>
       </c>
       <c r="Y108" s="3" t="inlineStr">
         <is>
-          <t>+3.0%</t>
+          <t>+13.2%</t>
         </is>
       </c>
       <c r="Z108" s="3" t="n">
-        <v>49.24</v>
+        <v>113.76</v>
       </c>
       <c r="AA108" s="3" t="inlineStr"/>
       <c r="AB108" s="3" t="inlineStr">
@@ -13126,37 +13124,37 @@
       </c>
       <c r="AC108" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 54.70 | KP2: MA50 aktuell 43.73 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
+          <t>KP1: 52W-Hoch 126.38 | KP2: MA50 aktuell 104.08 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Corcept Therapeutics Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
-        <v>111.62</v>
+        <v>524.14</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>126.38</v>
+        <v>534.99</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>28.66</v>
+        <v>110.22</v>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
@@ -13165,12 +13163,12 @@
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>✓ +32%</t>
+          <t>✓ +58%</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>+24%</t>
+          <t>+273%</t>
         </is>
       </c>
       <c r="K109" s="3" t="inlineStr">
@@ -13179,15 +13177,15 @@
         </is>
       </c>
       <c r="L109" s="3" t="n">
-        <v>126.51</v>
+        <v>535.52</v>
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
-          <t>+13.3%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="N109" s="3" t="n">
-        <v>117.53</v>
+        <v>497.54</v>
       </c>
       <c r="O109" s="3" t="inlineStr"/>
       <c r="P109" s="3" t="inlineStr">
@@ -13201,15 +13199,15 @@
         </is>
       </c>
       <c r="R109" s="3" t="n">
-        <v>104.6</v>
+        <v>441.65</v>
       </c>
       <c r="S109" s="3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="T109" s="3" t="n">
-        <v>98.87</v>
+        <v>417.48</v>
       </c>
       <c r="U109" s="3" t="inlineStr"/>
       <c r="V109" s="3" t="inlineStr">
@@ -13223,15 +13221,15 @@
         </is>
       </c>
       <c r="X109" s="3" t="n">
-        <v>126.39</v>
+        <v>535</v>
       </c>
       <c r="Y109" s="3" t="inlineStr">
         <is>
-          <t>+13.2%</t>
+          <t>+2.1%</t>
         </is>
       </c>
       <c r="Z109" s="3" t="n">
-        <v>113.76</v>
+        <v>481.5</v>
       </c>
       <c r="AA109" s="3" t="inlineStr"/>
       <c r="AB109" s="3" t="inlineStr">
@@ -13241,37 +13239,37 @@
       </c>
       <c r="AC109" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 126.38 | KP2: MA50 aktuell 104.08 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
+          <t>KP1: 52W-Hoch 534.99 | KP2: MA50 aktuell 439.45 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Okeanis Eco Tankers Corp</t>
         </is>
       </c>
       <c r="C110" s="3" t="n">
-        <v>524.14</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>534.96</v>
+        <v>71.77</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>110.22</v>
+        <v>27.59</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G110" s="3" t="n">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
@@ -13280,12 +13278,12 @@
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>✓ +58%</t>
+          <t>✓ +239%</t>
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>+273%</t>
+          <t>+606%</t>
         </is>
       </c>
       <c r="K110" s="3" t="inlineStr">
@@ -13294,15 +13292,15 @@
         </is>
       </c>
       <c r="L110" s="3" t="n">
-        <v>535.49</v>
+        <v>71.84</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="N110" s="3" t="n">
-        <v>497.51</v>
+        <v>66.75</v>
       </c>
       <c r="O110" s="3" t="inlineStr"/>
       <c r="P110" s="3" t="inlineStr">
@@ -13316,15 +13314,15 @@
         </is>
       </c>
       <c r="R110" s="3" t="n">
-        <v>441.65</v>
+        <v>59.92</v>
       </c>
       <c r="S110" s="3" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="T110" s="3" t="n">
-        <v>417.48</v>
+        <v>56.64</v>
       </c>
       <c r="U110" s="3" t="inlineStr"/>
       <c r="V110" s="3" t="inlineStr">
@@ -13338,15 +13336,15 @@
         </is>
       </c>
       <c r="X110" s="3" t="n">
-        <v>534.97</v>
+        <v>71.78</v>
       </c>
       <c r="Y110" s="3" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+0.5%</t>
         </is>
       </c>
       <c r="Z110" s="3" t="n">
-        <v>481.48</v>
+        <v>64.61</v>
       </c>
       <c r="AA110" s="3" t="inlineStr"/>
       <c r="AB110" s="3" t="inlineStr">
@@ -13356,37 +13354,37 @@
       </c>
       <c r="AC110" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 534.96 | KP2: MA50 aktuell 439.45 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
+          <t>KP1: 52W-Hoch 71.77 | KP2: MA50 aktuell 59.62 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Okeanis Eco Tankers Corp</t>
+          <t>Hewlett Packard Enterprise Co</t>
         </is>
       </c>
       <c r="C111" s="3" t="n">
-        <v>71.43000000000001</v>
+        <v>52</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>71.77</v>
+        <v>64.25</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>27.59</v>
+        <v>19.84</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
@@ -13395,12 +13393,12 @@
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>✓ +239%</t>
+          <t>✓ +34%</t>
         </is>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>+606%</t>
+          <t>+410%</t>
         </is>
       </c>
       <c r="K111" s="3" t="inlineStr">
@@ -13409,15 +13407,15 @@
         </is>
       </c>
       <c r="L111" s="3" t="n">
-        <v>71.84</v>
+        <v>64.31</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>+23.7%</t>
         </is>
       </c>
       <c r="N111" s="3" t="n">
-        <v>66.75</v>
+        <v>59.75</v>
       </c>
       <c r="O111" s="3" t="inlineStr"/>
       <c r="P111" s="3" t="inlineStr">
@@ -13427,81 +13425,81 @@
       </c>
       <c r="Q111" s="3" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="R111" s="3" t="n">
-        <v>59.92</v>
+        <v>63.45</v>
       </c>
       <c r="S111" s="3" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>+22.0%</t>
         </is>
       </c>
       <c r="T111" s="3" t="n">
-        <v>56.64</v>
+        <v>57.11</v>
       </c>
       <c r="U111" s="3" t="inlineStr"/>
       <c r="V111" s="3" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="W111" s="3" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="X111" s="3" t="n">
-        <v>71.78</v>
+        <v>50.26</v>
       </c>
       <c r="Y111" s="3" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="Z111" s="3" t="n">
-        <v>64.61</v>
+        <v>47.51</v>
       </c>
       <c r="AA111" s="3" t="inlineStr"/>
       <c r="AB111" s="3" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="AC111" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 71.77 | KP2: MA50 aktuell 59.62 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
+          <t>KP1: 52W-Hoch 64.25 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 50.01 (nur bei intaktem Trend nutzen)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>INBX</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise Co</t>
+          <t>Inhibrx Biosciences Inc</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
-        <v>52</v>
+        <v>121.17</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>64.25</v>
+        <v>155.29</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>19.84</v>
+        <v>26.19</v>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="G112" s="3" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
@@ -13510,12 +13508,12 @@
       </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>✓ +34%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>+410%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr">
@@ -13524,15 +13522,15 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>64.31</v>
+        <v>155.45</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>+23.7%</t>
+          <t>+28.3%</t>
         </is>
       </c>
       <c r="N112" s="3" t="n">
-        <v>59.75</v>
+        <v>144.42</v>
       </c>
       <c r="O112" s="3" t="inlineStr"/>
       <c r="P112" s="3" t="inlineStr">
@@ -13546,15 +13544,15 @@
         </is>
       </c>
       <c r="R112" s="3" t="n">
-        <v>63.45</v>
+        <v>131.02</v>
       </c>
       <c r="S112" s="3" t="inlineStr">
         <is>
-          <t>+22.0%</t>
+          <t>+8.1%</t>
         </is>
       </c>
       <c r="T112" s="3" t="n">
-        <v>57.11</v>
+        <v>117.92</v>
       </c>
       <c r="U112" s="3" t="inlineStr"/>
       <c r="V112" s="3" t="inlineStr">
@@ -13568,15 +13566,15 @@
         </is>
       </c>
       <c r="X112" s="3" t="n">
-        <v>50.26</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="Y112" s="3" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Z112" s="3" t="n">
-        <v>47.51</v>
+        <v>92.33</v>
       </c>
       <c r="AA112" s="3" t="inlineStr"/>
       <c r="AB112" s="3" t="inlineStr">
@@ -13586,37 +13584,37 @@
       </c>
       <c r="AC112" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 64.25 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 50.01 (nur bei intaktem Trend nutzen)</t>
+          <t>KP1: 52W-Hoch 155.29 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 97.19 (nur bei intaktem Trend nutzen)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>INBX</t>
+          <t>KNSA</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Inhibrx Biosciences Inc</t>
+          <t>Kiniksa Pharmaceuticals International Plc</t>
         </is>
       </c>
       <c r="C113" s="3" t="n">
-        <v>121.17</v>
+        <v>77.91</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>155.29</v>
+        <v>82.94</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>26.19</v>
+        <v>35.12</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
@@ -13625,12 +13623,12 @@
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>✓ +55%</t>
         </is>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+30%</t>
         </is>
       </c>
       <c r="K113" s="3" t="inlineStr">
@@ -13639,15 +13637,15 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>155.45</v>
+        <v>83.02</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>+28.3%</t>
+          <t>+6.6%</t>
         </is>
       </c>
       <c r="N113" s="3" t="n">
-        <v>144.42</v>
+        <v>77.13</v>
       </c>
       <c r="O113" s="3" t="inlineStr"/>
       <c r="P113" s="3" t="inlineStr">
@@ -13661,15 +13659,15 @@
         </is>
       </c>
       <c r="R113" s="3" t="n">
-        <v>131.02</v>
+        <v>81.58</v>
       </c>
       <c r="S113" s="3" t="inlineStr">
         <is>
-          <t>+8.1%</t>
+          <t>+4.7%</t>
         </is>
       </c>
       <c r="T113" s="3" t="n">
-        <v>117.92</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="U113" s="3" t="inlineStr"/>
       <c r="V113" s="3" t="inlineStr">
@@ -13683,15 +13681,15 @@
         </is>
       </c>
       <c r="X113" s="3" t="n">
-        <v>97.68000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="Y113" s="3" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z113" s="3" t="n">
-        <v>92.33</v>
+        <v>68.28</v>
       </c>
       <c r="AA113" s="3" t="inlineStr"/>
       <c r="AB113" s="3" t="inlineStr">
@@ -13701,37 +13699,37 @@
       </c>
       <c r="AC113" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 155.29 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 97.19 (nur bei intaktem Trend nutzen)</t>
+          <t>KP1: 52W-Hoch 82.94 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 71.87 (nur bei intaktem Trend nutzen)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>KNSA</t>
+          <t>KYMR</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Kiniksa Pharmaceuticals International Plc</t>
+          <t>Kymera Therapeutics Inc</t>
         </is>
       </c>
       <c r="C114" s="3" t="n">
-        <v>77.91</v>
+        <v>117.39</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>82.94</v>
+        <v>130.05</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>35.12</v>
+        <v>42.22</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="G114" s="3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
@@ -13740,12 +13738,12 @@
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>✓ +55%</t>
+          <t>✓ +466%</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>+30%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr">
@@ -13754,15 +13752,15 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>83.02</v>
+        <v>130.18</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>+6.6%</t>
+          <t>+10.9%</t>
         </is>
       </c>
       <c r="N114" s="3" t="n">
-        <v>77.13</v>
+        <v>120.95</v>
       </c>
       <c r="O114" s="3" t="inlineStr"/>
       <c r="P114" s="3" t="inlineStr">
@@ -13776,15 +13774,15 @@
         </is>
       </c>
       <c r="R114" s="3" t="n">
-        <v>81.58</v>
+        <v>127.86</v>
       </c>
       <c r="S114" s="3" t="inlineStr">
         <is>
-          <t>+4.7%</t>
+          <t>+8.9%</t>
         </is>
       </c>
       <c r="T114" s="3" t="n">
-        <v>74.98999999999999</v>
+        <v>115.08</v>
       </c>
       <c r="U114" s="3" t="inlineStr"/>
       <c r="V114" s="3" t="inlineStr">
@@ -13798,15 +13796,15 @@
         </is>
       </c>
       <c r="X114" s="3" t="n">
-        <v>72.23</v>
+        <v>114.62</v>
       </c>
       <c r="Y114" s="3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="Z114" s="3" t="n">
-        <v>68.28</v>
+        <v>108.35</v>
       </c>
       <c r="AA114" s="3" t="inlineStr"/>
       <c r="AB114" s="3" t="inlineStr">
@@ -13816,37 +13814,37 @@
       </c>
       <c r="AC114" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 82.94 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 71.87 (nur bei intaktem Trend nutzen)</t>
+          <t>KP1: 52W-Hoch 130.05 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 114.05 (nur bei intaktem Trend nutzen)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>KYMR</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Kymera Therapeutics Inc</t>
+          <t>Okta Inc</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
-        <v>117.39</v>
+        <v>170.6</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>130.05</v>
+        <v>174.85</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>42.22</v>
+        <v>62.66</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
@@ -13855,12 +13853,12 @@
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>✓ +466%</t>
+          <t>✗ +11%</t>
         </is>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+76%</t>
         </is>
       </c>
       <c r="K115" s="3" t="inlineStr">
@@ -13869,15 +13867,15 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>130.18</v>
+        <v>175.02</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>+10.9%</t>
+          <t>+2.6%</t>
         </is>
       </c>
       <c r="N115" s="3" t="n">
-        <v>120.95</v>
+        <v>162.61</v>
       </c>
       <c r="O115" s="3" t="inlineStr"/>
       <c r="P115" s="3" t="inlineStr">
@@ -13887,81 +13885,81 @@
       </c>
       <c r="Q115" s="3" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="R115" s="3" t="n">
-        <v>127.86</v>
+        <v>146.67</v>
       </c>
       <c r="S115" s="3" t="inlineStr">
         <is>
-          <t>+8.9%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="T115" s="3" t="n">
-        <v>115.08</v>
+        <v>138.65</v>
       </c>
       <c r="U115" s="3" t="inlineStr"/>
       <c r="V115" s="3" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="W115" s="3" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="X115" s="3" t="n">
-        <v>114.62</v>
+        <v>174.86</v>
       </c>
       <c r="Y115" s="3" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>+2.5%</t>
         </is>
       </c>
       <c r="Z115" s="3" t="n">
-        <v>108.35</v>
+        <v>157.38</v>
       </c>
       <c r="AA115" s="3" t="inlineStr"/>
       <c r="AB115" s="3" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="AC115" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 130.05 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 114.05 (nur bei intaktem Trend nutzen)</t>
+          <t>KP1: 52W-Hoch 174.85 | KP2: MA50 aktuell 145.94 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>PTGX</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Okta Inc</t>
+          <t>Protagonist Therapeutics Inc</t>
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>170.6</v>
+        <v>145.72</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>174.85</v>
+        <v>160.81</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>62.66</v>
+        <v>54.5</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="G116" s="3" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
@@ -13970,12 +13968,12 @@
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>✗ +11%</t>
+          <t>✓ +3749%</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>+76%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K116" s="3" t="inlineStr">
@@ -13984,15 +13982,15 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>175.02</v>
+        <v>160.97</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>+2.6%</t>
+          <t>+10.5%</t>
         </is>
       </c>
       <c r="N116" s="3" t="n">
-        <v>162.61</v>
+        <v>149.55</v>
       </c>
       <c r="O116" s="3" t="inlineStr"/>
       <c r="P116" s="3" t="inlineStr">
@@ -14006,15 +14004,15 @@
         </is>
       </c>
       <c r="R116" s="3" t="n">
-        <v>146.67</v>
+        <v>141.7</v>
       </c>
       <c r="S116" s="3" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="T116" s="3" t="n">
-        <v>138.65</v>
+        <v>133.95</v>
       </c>
       <c r="U116" s="3" t="inlineStr"/>
       <c r="V116" s="3" t="inlineStr">
@@ -14028,15 +14026,15 @@
         </is>
       </c>
       <c r="X116" s="3" t="n">
-        <v>174.86</v>
+        <v>160.82</v>
       </c>
       <c r="Y116" s="3" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>+10.4%</t>
         </is>
       </c>
       <c r="Z116" s="3" t="n">
-        <v>157.38</v>
+        <v>144.74</v>
       </c>
       <c r="AA116" s="3" t="inlineStr"/>
       <c r="AB116" s="3" t="inlineStr">
@@ -14046,37 +14044,37 @@
       </c>
       <c r="AC116" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 174.85 | KP2: MA50 aktuell 145.94 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
+          <t>KP1: 52W-Hoch 160.81 | KP2: MA50 aktuell 141.00 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>PTGX</t>
+          <t>RNG</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Protagonist Therapeutics Inc</t>
+          <t>RingCentral Inc</t>
         </is>
       </c>
       <c r="C117" s="3" t="n">
-        <v>145.72</v>
+        <v>73.39</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>160.81</v>
+        <v>77.95</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>54.5</v>
+        <v>24.14</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="G117" s="3" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
@@ -14085,12 +14083,12 @@
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>✓ +3749%</t>
+          <t>✗ +6%</t>
         </is>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+221%</t>
         </is>
       </c>
       <c r="K117" s="3" t="inlineStr">
@@ -14099,15 +14097,15 @@
         </is>
       </c>
       <c r="L117" s="3" t="n">
-        <v>160.97</v>
+        <v>78.03</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>+10.5%</t>
+          <t>+6.3%</t>
         </is>
       </c>
       <c r="N117" s="3" t="n">
-        <v>149.55</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="O117" s="3" t="inlineStr"/>
       <c r="P117" s="3" t="inlineStr">
@@ -14121,15 +14119,15 @@
         </is>
       </c>
       <c r="R117" s="3" t="n">
-        <v>141.7</v>
+        <v>55.11</v>
       </c>
       <c r="S117" s="3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="T117" s="3" t="n">
-        <v>133.95</v>
+        <v>52.09</v>
       </c>
       <c r="U117" s="3" t="inlineStr"/>
       <c r="V117" s="3" t="inlineStr">
@@ -14143,15 +14141,15 @@
         </is>
       </c>
       <c r="X117" s="3" t="n">
-        <v>160.82</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="Y117" s="3" t="inlineStr">
         <is>
-          <t>+10.4%</t>
+          <t>+6.2%</t>
         </is>
       </c>
       <c r="Z117" s="3" t="n">
-        <v>144.74</v>
+        <v>70.17</v>
       </c>
       <c r="AA117" s="3" t="inlineStr"/>
       <c r="AB117" s="3" t="inlineStr">
@@ -14161,33 +14159,33 @@
       </c>
       <c r="AC117" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 160.81 | KP2: MA50 aktuell 141.00 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
+          <t>KP1: 52W-Hoch 77.95 | KP2: MA50 aktuell 54.84 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>RNG</t>
+          <t>TVTX</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>RingCentral Inc</t>
+          <t>Travere Therapeutics Inc</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>73.39</v>
+        <v>65.28</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>77.95</v>
+        <v>68.03</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>24.14</v>
+        <v>20.84</v>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="G118" s="3" t="n">
@@ -14200,12 +14198,12 @@
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>✗ +6%</t>
+          <t>✓ +48%</t>
         </is>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>+221%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K118" s="3" t="inlineStr">
@@ -14214,15 +14212,15 @@
         </is>
       </c>
       <c r="L118" s="3" t="n">
-        <v>78.03</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>+6.3%</t>
+          <t>+4.3%</t>
         </is>
       </c>
       <c r="N118" s="3" t="n">
-        <v>72.48999999999999</v>
+        <v>63.27</v>
       </c>
       <c r="O118" s="3" t="inlineStr"/>
       <c r="P118" s="3" t="inlineStr">
@@ -14236,15 +14234,15 @@
         </is>
       </c>
       <c r="R118" s="3" t="n">
-        <v>55.11</v>
+        <v>60.57</v>
       </c>
       <c r="S118" s="3" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="T118" s="3" t="n">
-        <v>52.09</v>
+        <v>57.25</v>
       </c>
       <c r="U118" s="3" t="inlineStr"/>
       <c r="V118" s="3" t="inlineStr">
@@ -14258,15 +14256,15 @@
         </is>
       </c>
       <c r="X118" s="3" t="n">
-        <v>77.95999999999999</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="Y118" s="3" t="inlineStr">
         <is>
-          <t>+6.2%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="Z118" s="3" t="n">
-        <v>70.17</v>
+        <v>61.24</v>
       </c>
       <c r="AA118" s="3" t="inlineStr"/>
       <c r="AB118" s="3" t="inlineStr">
@@ -14276,37 +14274,37 @@
       </c>
       <c r="AC118" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 77.95 | KP2: MA50 aktuell 54.84 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
+          <t>KP1: 52W-Hoch 68.03 | KP2: MA50 aktuell 60.26 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>TVTX</t>
+          <t>TWST</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Travere Therapeutics Inc</t>
+          <t>Twist Bioscience Corp</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
-        <v>65.28</v>
+        <v>124.72</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>68.03</v>
+        <v>155.44</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>20.84</v>
+        <v>23.3</v>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="G119" s="3" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
@@ -14315,7 +14313,7 @@
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>✓ +48%</t>
+          <t>✗ +23%</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr">
@@ -14329,15 +14327,15 @@
         </is>
       </c>
       <c r="L119" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>155.6</v>
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
-          <t>+4.3%</t>
+          <t>+24.8%</t>
         </is>
       </c>
       <c r="N119" s="3" t="n">
-        <v>63.27</v>
+        <v>144.56</v>
       </c>
       <c r="O119" s="3" t="inlineStr"/>
       <c r="P119" s="3" t="inlineStr">
@@ -14351,15 +14349,15 @@
         </is>
       </c>
       <c r="R119" s="3" t="n">
-        <v>60.57</v>
+        <v>111.47</v>
       </c>
       <c r="S119" s="3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="T119" s="3" t="n">
-        <v>57.25</v>
+        <v>105.37</v>
       </c>
       <c r="U119" s="3" t="inlineStr"/>
       <c r="V119" s="3" t="inlineStr">
@@ -14373,15 +14371,15 @@
         </is>
       </c>
       <c r="X119" s="3" t="n">
-        <v>68.04000000000001</v>
+        <v>155.45</v>
       </c>
       <c r="Y119" s="3" t="inlineStr">
         <is>
-          <t>+4.2%</t>
+          <t>+24.6%</t>
         </is>
       </c>
       <c r="Z119" s="3" t="n">
-        <v>61.24</v>
+        <v>139.91</v>
       </c>
       <c r="AA119" s="3" t="inlineStr"/>
       <c r="AB119" s="3" t="inlineStr">
@@ -14391,166 +14389,166 @@
       </c>
       <c r="AC119" s="3" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 68.03 | KP2: MA50 aktuell 60.26 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
+          <t>KP1: 52W-Hoch 155.44 | KP2: MA50 aktuell 110.92 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>TWST</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>Twist Bioscience Corp</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="n">
-        <v>124.72</v>
-      </c>
-      <c r="D120" s="3" t="n">
-        <v>155.44</v>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>-19.8%</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>✓ 8/8</t>
-        </is>
-      </c>
-      <c r="I120" s="3" t="inlineStr">
-        <is>
-          <t>✗ +23%</t>
-        </is>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>ANDG</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>Andersen Group Inc</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>✗ 0/8</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>✗ +24%</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K120" s="3" t="inlineStr">
+      <c r="K120" s="4" t="inlineStr">
         <is>
           <t>Fallback: 52W-Hoch-Breakout</t>
         </is>
       </c>
-      <c r="L120" s="3" t="n">
-        <v>155.6</v>
-      </c>
-      <c r="M120" s="3" t="inlineStr">
-        <is>
-          <t>+24.8%</t>
-        </is>
-      </c>
-      <c r="N120" s="3" t="n">
-        <v>144.56</v>
-      </c>
-      <c r="O120" s="3" t="inlineStr"/>
-      <c r="P120" s="3" t="inlineStr">
+      <c r="L120" s="4" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="M120" s="4" t="inlineStr">
+        <is>
+          <t>+2.5%</t>
+        </is>
+      </c>
+      <c r="N120" s="4" t="n">
+        <v>53.59</v>
+      </c>
+      <c r="O120" s="4" t="inlineStr"/>
+      <c r="P120" s="4" t="inlineStr">
         <is>
           <t>Kein Muster — generischer Breakout-Level</t>
         </is>
       </c>
-      <c r="Q120" s="3" t="inlineStr">
+      <c r="Q120" s="4" t="inlineStr">
         <is>
           <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
-      <c r="R120" s="3" t="n">
-        <v>111.47</v>
-      </c>
-      <c r="S120" s="3" t="inlineStr">
-        <is>
-          <t>-10.6%</t>
-        </is>
-      </c>
-      <c r="T120" s="3" t="n">
-        <v>105.37</v>
-      </c>
-      <c r="U120" s="3" t="inlineStr"/>
-      <c r="V120" s="3" t="inlineStr">
+      <c r="R120" s="4" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="S120" s="4" t="inlineStr">
+        <is>
+          <t>-16.8%</t>
+        </is>
+      </c>
+      <c r="T120" s="4" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="U120" s="4" t="inlineStr"/>
+      <c r="V120" s="4" t="inlineStr">
         <is>
           <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
-      <c r="W120" s="3" t="inlineStr">
+      <c r="W120" s="4" t="inlineStr">
         <is>
           <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
-      <c r="X120" s="3" t="n">
-        <v>155.45</v>
-      </c>
-      <c r="Y120" s="3" t="inlineStr">
-        <is>
-          <t>+24.6%</t>
-        </is>
-      </c>
-      <c r="Z120" s="3" t="n">
-        <v>139.91</v>
-      </c>
-      <c r="AA120" s="3" t="inlineStr"/>
-      <c r="AB120" s="3" t="inlineStr">
+      <c r="X120" s="4" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="Y120" s="4" t="inlineStr">
+        <is>
+          <t>+2.4%</t>
+        </is>
+      </c>
+      <c r="Z120" s="4" t="n">
+        <v>51.87</v>
+      </c>
+      <c r="AA120" s="4" t="inlineStr"/>
+      <c r="AB120" s="4" t="inlineStr">
         <is>
           <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
-      <c r="AC120" s="3" t="inlineStr">
-        <is>
-          <t>KP1: 52W-Hoch 155.44 | KP2: MA50 aktuell 110.92 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage</t>
+      <c r="AC120" s="4" t="inlineStr">
+        <is>
+          <t>KP1: 52W-Hoch 57.62 | KP2: MA50 aktuell 46.58 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: Zu wenig Historie für MA200</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>ANDG</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Andersen Group Inc</t>
+          <t>Abercrombie &amp; Fitch Co</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>56.26</v>
+        <v>149.67</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>57.62</v>
+        <v>154.58</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>18.12</v>
+        <v>65.45</v>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="G121" s="4" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>✗ 0/8</t>
+          <t>✗ 7/8</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>✗ +24%</t>
+          <t>✗ +5%</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+43%</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
@@ -14559,15 +14557,15 @@
         </is>
       </c>
       <c r="L121" s="4" t="n">
-        <v>57.68</v>
+        <v>154.73</v>
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>+3.4%</t>
         </is>
       </c>
       <c r="N121" s="4" t="n">
-        <v>53.59</v>
+        <v>143.76</v>
       </c>
       <c r="O121" s="4" t="inlineStr"/>
       <c r="P121" s="4" t="inlineStr">
@@ -14581,15 +14579,15 @@
         </is>
       </c>
       <c r="R121" s="4" t="n">
-        <v>46.81</v>
+        <v>107.98</v>
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="T121" s="4" t="n">
-        <v>44.25</v>
+        <v>102.07</v>
       </c>
       <c r="U121" s="4" t="inlineStr"/>
       <c r="V121" s="4" t="inlineStr">
@@ -14603,15 +14601,15 @@
         </is>
       </c>
       <c r="X121" s="4" t="n">
-        <v>57.63</v>
+        <v>154.59</v>
       </c>
       <c r="Y121" s="4" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>+3.3%</t>
         </is>
       </c>
       <c r="Z121" s="4" t="n">
-        <v>51.87</v>
+        <v>139.14</v>
       </c>
       <c r="AA121" s="4" t="inlineStr"/>
       <c r="AB121" s="4" t="inlineStr">
@@ -14621,51 +14619,51 @@
       </c>
       <c r="AC121" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 57.62 | KP2: MA50 aktuell 46.58 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: Zu wenig Historie für MA200</t>
+          <t>KP1: 52W-Hoch 154.58 | KP2: MA50 aktuell 107.44 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: MA150 &gt; MA200</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>ARGX</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Abercrombie &amp; Fitch Co</t>
+          <t>Argen X SE ADR</t>
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>149.67</v>
+        <v>1033.15</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>154.58</v>
+        <v>1072.75</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>65.45</v>
+        <v>661.85</v>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="G122" s="4" t="n">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>✗ 7/8</t>
+          <t>✗ 6/8</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>✗ +5%</t>
+          <t>✓ +59%</t>
         </is>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>+43%</t>
+          <t>+95%</t>
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr">
@@ -14674,15 +14672,15 @@
         </is>
       </c>
       <c r="L122" s="4" t="n">
-        <v>154.73</v>
+        <v>1073.82</v>
       </c>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>+3.9%</t>
         </is>
       </c>
       <c r="N122" s="4" t="n">
-        <v>143.76</v>
+        <v>997.66</v>
       </c>
       <c r="O122" s="4" t="inlineStr"/>
       <c r="P122" s="4" t="inlineStr">
@@ -14696,15 +14694,15 @@
         </is>
       </c>
       <c r="R122" s="4" t="n">
-        <v>107.98</v>
+        <v>930.04</v>
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="T122" s="4" t="n">
-        <v>102.07</v>
+        <v>879.14</v>
       </c>
       <c r="U122" s="4" t="inlineStr"/>
       <c r="V122" s="4" t="inlineStr">
@@ -14718,15 +14716,15 @@
         </is>
       </c>
       <c r="X122" s="4" t="n">
-        <v>154.59</v>
+        <v>1072.76</v>
       </c>
       <c r="Y122" s="4" t="inlineStr">
         <is>
-          <t>+3.3%</t>
+          <t>+3.8%</t>
         </is>
       </c>
       <c r="Z122" s="4" t="n">
-        <v>139.14</v>
+        <v>965.49</v>
       </c>
       <c r="AA122" s="4" t="inlineStr"/>
       <c r="AB122" s="4" t="inlineStr">
@@ -14736,37 +14734,37 @@
       </c>
       <c r="AC122" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 154.58 | KP2: MA50 aktuell 107.44 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: MA150 &gt; MA200</t>
+          <t>KP1: 52W-Hoch 1072.75 | KP2: MA50 aktuell 925.41 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: MA150 &gt; MA200; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>ARGX</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Argen X SE ADR</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>1033.15</v>
+        <v>1714.88</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>1072.75</v>
+        <v>1999.96</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>661.85</v>
+        <v>766.24</v>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="G123" s="4" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
@@ -14775,12 +14773,12 @@
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>✓ +59%</t>
+          <t>✗ +21%</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>+95%</t>
+          <t>+28%</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
@@ -14789,15 +14787,15 @@
         </is>
       </c>
       <c r="L123" s="4" t="n">
-        <v>1073.82</v>
+        <v>2001.96</v>
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>+3.9%</t>
+          <t>+16.7%</t>
         </is>
       </c>
       <c r="N123" s="4" t="n">
-        <v>997.66</v>
+        <v>1859.96</v>
       </c>
       <c r="O123" s="4" t="inlineStr"/>
       <c r="P123" s="4" t="inlineStr">
@@ -14807,95 +14805,95 @@
       </c>
       <c r="Q123" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="R123" s="4" t="n">
-        <v>930.04</v>
+        <v>1896.36</v>
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>+10.6%</t>
         </is>
       </c>
       <c r="T123" s="4" t="n">
-        <v>879.14</v>
+        <v>1706.73</v>
       </c>
       <c r="U123" s="4" t="inlineStr"/>
       <c r="V123" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="W123" s="4" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: MA50-Rückeroberung</t>
         </is>
       </c>
       <c r="X123" s="4" t="n">
-        <v>1072.76</v>
+        <v>1760.23</v>
       </c>
       <c r="Y123" s="4" t="inlineStr">
         <is>
-          <t>+3.8%</t>
+          <t>+2.6%</t>
         </is>
       </c>
       <c r="Z123" s="4" t="n">
-        <v>965.49</v>
+        <v>1646.39</v>
       </c>
       <c r="AA123" s="4" t="inlineStr"/>
       <c r="AB123" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kurs UNTER MA50 — erst bei Reclaim interessant</t>
         </is>
       </c>
       <c r="AC123" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 1072.75 | KP2: MA50 aktuell 925.41 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: MA150 &gt; MA200; RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 1999.96 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 1751.47; Kauf erst wenn Schlusskurs drüber | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>ASST</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>Strive Inc</t>
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>1714.88</v>
+        <v>27.14</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>1999.96</v>
+        <v>252</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>766.24</v>
+        <v>7.02</v>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-89.2%</t>
         </is>
       </c>
       <c r="G124" s="4" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>✗ 6/8</t>
+          <t>✗ 4/8</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>✗ +21%</t>
+          <t>✓ +95%</t>
         </is>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>+28%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr">
@@ -14904,15 +14902,15 @@
         </is>
       </c>
       <c r="L124" s="4" t="n">
-        <v>2001.96</v>
+        <v>252.25</v>
       </c>
       <c r="M124" s="4" t="inlineStr">
         <is>
-          <t>+16.7%</t>
+          <t>+829.4%</t>
         </is>
       </c>
       <c r="N124" s="4" t="n">
-        <v>1859.96</v>
+        <v>234.36</v>
       </c>
       <c r="O124" s="4" t="inlineStr"/>
       <c r="P124" s="4" t="inlineStr">
@@ -14926,15 +14924,15 @@
         </is>
       </c>
       <c r="R124" s="4" t="n">
-        <v>1896.36</v>
+        <v>27.36</v>
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>+10.6%</t>
+          <t>+0.8%</t>
         </is>
       </c>
       <c r="T124" s="4" t="n">
-        <v>1706.73</v>
+        <v>24.63</v>
       </c>
       <c r="U124" s="4" t="inlineStr"/>
       <c r="V124" s="4" t="inlineStr">
@@ -14944,73 +14942,73 @@
       </c>
       <c r="W124" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Rückeroberung</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="X124" s="4" t="n">
-        <v>1760.23</v>
+        <v>14.78</v>
       </c>
       <c r="Y124" s="4" t="inlineStr">
         <is>
-          <t>+2.6%</t>
+          <t>-45.5%</t>
         </is>
       </c>
       <c r="Z124" s="4" t="n">
-        <v>1646.39</v>
+        <v>13.97</v>
       </c>
       <c r="AA124" s="4" t="inlineStr"/>
       <c r="AB124" s="4" t="inlineStr">
         <is>
-          <t>Kurs UNTER MA50 — erst bei Reclaim interessant</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="AC124" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 1999.96 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 1751.47; Kauf erst wenn Schlusskurs drüber | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 252.00 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 14.71 (nur bei intaktem Trend nutzen) | TT fehlt: MA150 &gt; MA200; MA200 steigt (≥1 Monat); MA50 &gt; MA150 &amp; MA200</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>ASST</t>
+          <t>ATRO</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Strive Inc</t>
+          <t>Astronics Corp</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>27.14</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>252</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>7.02</v>
+        <v>29.43</v>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>-89.2%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="G125" s="4" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>✗ 4/8</t>
+          <t>✗ 7/8</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>✓ +95%</t>
+          <t>✓ +27%</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+2400%</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
@@ -15019,15 +15017,15 @@
         </is>
       </c>
       <c r="L125" s="4" t="n">
-        <v>252.25</v>
+        <v>94.55</v>
       </c>
       <c r="M125" s="4" t="inlineStr">
         <is>
-          <t>+829.4%</t>
+          <t>+24.0%</t>
         </is>
       </c>
       <c r="N125" s="4" t="n">
-        <v>234.36</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="O125" s="4" t="inlineStr"/>
       <c r="P125" s="4" t="inlineStr">
@@ -15037,95 +15035,95 @@
       </c>
       <c r="Q125" s="4" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="R125" s="4" t="n">
-        <v>27.36</v>
+        <v>75.63</v>
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="T125" s="4" t="n">
-        <v>24.63</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="U125" s="4" t="inlineStr"/>
       <c r="V125" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="W125" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="X125" s="4" t="n">
-        <v>14.78</v>
+        <v>94.47</v>
       </c>
       <c r="Y125" s="4" t="inlineStr">
         <is>
-          <t>-45.5%</t>
+          <t>+23.9%</t>
         </is>
       </c>
       <c r="Z125" s="4" t="n">
-        <v>13.97</v>
+        <v>85.03</v>
       </c>
       <c r="AA125" s="4" t="inlineStr"/>
       <c r="AB125" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="AC125" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 252.00 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 14.71 (nur bei intaktem Trend nutzen) | TT fehlt: MA150 &gt; MA200; MA200 steigt (≥1 Monat); MA50 &gt; MA150 &amp; MA200</t>
+          <t>KP1: 52W-Hoch 94.46 | KP2: MA50 aktuell 75.25 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>ATRO</t>
+          <t>CNXC</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>Astronics Corp</t>
+          <t>Concentrix Corp</t>
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>76.26000000000001</v>
+        <v>32.16</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>94.45999999999999</v>
+        <v>57.88</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>29.43</v>
+        <v>19.12</v>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-44.4%</t>
         </is>
       </c>
       <c r="G126" s="4" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>✗ 7/8</t>
+          <t>✗ 3/8</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
-          <t>✓ +27%</t>
+          <t>✗ +2%</t>
         </is>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>+2400%</t>
+          <t>+36%</t>
         </is>
       </c>
       <c r="K126" s="4" t="inlineStr">
@@ -15134,15 +15132,15 @@
         </is>
       </c>
       <c r="L126" s="4" t="n">
-        <v>94.55</v>
+        <v>57.93</v>
       </c>
       <c r="M126" s="4" t="inlineStr">
         <is>
-          <t>+24.0%</t>
+          <t>+80.1%</t>
         </is>
       </c>
       <c r="N126" s="4" t="n">
-        <v>87.84999999999999</v>
+        <v>53.82</v>
       </c>
       <c r="O126" s="4" t="inlineStr"/>
       <c r="P126" s="4" t="inlineStr">
@@ -15152,95 +15150,95 @@
       </c>
       <c r="Q126" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="R126" s="4" t="n">
-        <v>75.63</v>
+        <v>33.85</v>
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>+5.3%</t>
         </is>
       </c>
       <c r="T126" s="4" t="n">
-        <v>71.48999999999999</v>
+        <v>30.47</v>
       </c>
       <c r="U126" s="4" t="inlineStr"/>
       <c r="V126" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="W126" s="4" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="X126" s="4" t="n">
-        <v>94.47</v>
+        <v>25.57</v>
       </c>
       <c r="Y126" s="4" t="inlineStr">
         <is>
-          <t>+23.9%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="Z126" s="4" t="n">
-        <v>85.03</v>
+        <v>24.17</v>
       </c>
       <c r="AA126" s="4" t="inlineStr"/>
       <c r="AB126" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="AC126" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 94.46 | KP2: MA50 aktuell 75.25 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 57.88 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 25.44 (nur bei intaktem Trend nutzen) | TT fehlt: MA150 &gt; MA200; MA200 steigt (≥1 Monat); MA50 &gt; MA150 &amp; MA200</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>DGII</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Concentrix Corp</t>
+          <t>Digi International Inc</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>32.16</v>
+        <v>69.36</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>57.88</v>
+        <v>86.84</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>19.12</v>
+        <v>33.74</v>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>-44.4%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="G127" s="4" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>✗ 3/8</t>
+          <t>✗ 6/8</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>✗ +2%</t>
+          <t>✓ +29%</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>+36%</t>
+          <t>+48%</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
@@ -15249,15 +15247,15 @@
         </is>
       </c>
       <c r="L127" s="4" t="n">
-        <v>57.93</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="M127" s="4" t="inlineStr">
         <is>
-          <t>+80.1%</t>
+          <t>+25.3%</t>
         </is>
       </c>
       <c r="N127" s="4" t="n">
-        <v>53.82</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="O127" s="4" t="inlineStr"/>
       <c r="P127" s="4" t="inlineStr">
@@ -15271,15 +15269,15 @@
         </is>
       </c>
       <c r="R127" s="4" t="n">
-        <v>33.85</v>
+        <v>86.03</v>
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>+5.3%</t>
+          <t>+24.0%</t>
         </is>
       </c>
       <c r="T127" s="4" t="n">
-        <v>30.47</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="U127" s="4" t="inlineStr"/>
       <c r="V127" s="4" t="inlineStr">
@@ -15289,73 +15287,73 @@
       </c>
       <c r="W127" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: MA50-Rückeroberung</t>
         </is>
       </c>
       <c r="X127" s="4" t="n">
-        <v>25.57</v>
+        <v>73.14</v>
       </c>
       <c r="Y127" s="4" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>+5.4%</t>
         </is>
       </c>
       <c r="Z127" s="4" t="n">
-        <v>24.17</v>
+        <v>68.41</v>
       </c>
       <c r="AA127" s="4" t="inlineStr"/>
       <c r="AB127" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kurs UNTER MA50 — erst bei Reclaim interessant</t>
         </is>
       </c>
       <c r="AC127" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 57.88 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 25.44 (nur bei intaktem Trend nutzen) | TT fehlt: MA150 &gt; MA200; MA200 steigt (≥1 Monat); MA50 &gt; MA150 &amp; MA200</t>
+          <t>KP1: 52W-Hoch 86.84 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 72.77; Kauf erst wenn Schlusskurs drüber | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>DGII</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Digi International Inc</t>
+          <t>EOG Resources Inc</t>
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>69.36</v>
+        <v>145.19</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>86.84</v>
+        <v>153.67</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>33.74</v>
+        <v>101.59</v>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="G128" s="4" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>✗ 6/8</t>
+          <t>✗ 7/8</t>
         </is>
       </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t>✓ +29%</t>
+          <t>✓ +59%</t>
         </is>
       </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>+48%</t>
+          <t>+109%</t>
         </is>
       </c>
       <c r="K128" s="4" t="inlineStr">
@@ -15364,15 +15362,15 @@
         </is>
       </c>
       <c r="L128" s="4" t="n">
-        <v>86.93000000000001</v>
+        <v>153.82</v>
       </c>
       <c r="M128" s="4" t="inlineStr">
         <is>
-          <t>+25.3%</t>
+          <t>+5.9%</t>
         </is>
       </c>
       <c r="N128" s="4" t="n">
-        <v>80.76000000000001</v>
+        <v>142.91</v>
       </c>
       <c r="O128" s="4" t="inlineStr"/>
       <c r="P128" s="4" t="inlineStr">
@@ -15382,95 +15380,95 @@
       </c>
       <c r="Q128" s="4" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="R128" s="4" t="n">
-        <v>86.03</v>
+        <v>142.24</v>
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>+24.0%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="T128" s="4" t="n">
-        <v>77.43000000000001</v>
+        <v>134.46</v>
       </c>
       <c r="U128" s="4" t="inlineStr"/>
       <c r="V128" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="W128" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Rückeroberung</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="X128" s="4" t="n">
-        <v>73.14</v>
+        <v>153.68</v>
       </c>
       <c r="Y128" s="4" t="inlineStr">
         <is>
-          <t>+5.4%</t>
+          <t>+5.8%</t>
         </is>
       </c>
       <c r="Z128" s="4" t="n">
-        <v>68.41</v>
+        <v>138.32</v>
       </c>
       <c r="AA128" s="4" t="inlineStr"/>
       <c r="AB128" s="4" t="inlineStr">
         <is>
-          <t>Kurs UNTER MA50 — erst bei Reclaim interessant</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="AC128" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 86.84 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 72.77; Kauf erst wenn Schlusskurs drüber | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 153.67 | KP2: MA50 aktuell 141.53 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>ESTC</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>EOG Resources Inc</t>
+          <t>Elastic N.V</t>
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>145.19</v>
+        <v>91.81</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>153.67</v>
+        <v>108</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>101.59</v>
+        <v>42.05</v>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="G129" s="4" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>✗ 7/8</t>
+          <t>✗ 5/8</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>✓ +59%</t>
+          <t>✗ +15%</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>+109%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
@@ -15479,15 +15477,15 @@
         </is>
       </c>
       <c r="L129" s="4" t="n">
-        <v>153.82</v>
+        <v>108.11</v>
       </c>
       <c r="M129" s="4" t="inlineStr">
         <is>
-          <t>+5.9%</t>
+          <t>+17.8%</t>
         </is>
       </c>
       <c r="N129" s="4" t="n">
-        <v>142.91</v>
+        <v>100.44</v>
       </c>
       <c r="O129" s="4" t="inlineStr"/>
       <c r="P129" s="4" t="inlineStr">
@@ -15501,15 +15499,15 @@
         </is>
       </c>
       <c r="R129" s="4" t="n">
-        <v>142.24</v>
+        <v>72.2</v>
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-21.4%</t>
         </is>
       </c>
       <c r="T129" s="4" t="n">
-        <v>134.46</v>
+        <v>68.25</v>
       </c>
       <c r="U129" s="4" t="inlineStr"/>
       <c r="V129" s="4" t="inlineStr">
@@ -15523,15 +15521,15 @@
         </is>
       </c>
       <c r="X129" s="4" t="n">
-        <v>153.68</v>
+        <v>108.01</v>
       </c>
       <c r="Y129" s="4" t="inlineStr">
         <is>
-          <t>+5.8%</t>
+          <t>+17.6%</t>
         </is>
       </c>
       <c r="Z129" s="4" t="n">
-        <v>138.32</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="AA129" s="4" t="inlineStr"/>
       <c r="AB129" s="4" t="inlineStr">
@@ -15541,46 +15539,46 @@
       </c>
       <c r="AC129" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 153.67 | KP2: MA50 aktuell 141.53 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 108.00 | KP2: MA50 aktuell 71.84 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: MA150 &gt; MA200; MA200 steigt (≥1 Monat); RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>ESTC</t>
+          <t>FIG</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Elastic N.V</t>
+          <t>Figma Inc</t>
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>91.81</v>
+        <v>24.12</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>108</v>
+        <v>71.48</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>42.05</v>
+        <v>16.6</v>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-66.3%</t>
         </is>
       </c>
       <c r="G130" s="4" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>✗ 5/8</t>
+          <t>✗ 1/8</t>
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>✗ +15%</t>
+          <t>✓ +48%</t>
         </is>
       </c>
       <c r="J130" s="4" t="inlineStr">
@@ -15594,15 +15592,15 @@
         </is>
       </c>
       <c r="L130" s="4" t="n">
-        <v>108.11</v>
+        <v>71.55</v>
       </c>
       <c r="M130" s="4" t="inlineStr">
         <is>
-          <t>+17.8%</t>
+          <t>+196.6%</t>
         </is>
       </c>
       <c r="N130" s="4" t="n">
-        <v>100.44</v>
+        <v>66.48</v>
       </c>
       <c r="O130" s="4" t="inlineStr"/>
       <c r="P130" s="4" t="inlineStr">
@@ -15612,95 +15610,95 @@
       </c>
       <c r="Q130" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="R130" s="4" t="n">
-        <v>72.2</v>
+        <v>31.23</v>
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>+29.5%</t>
         </is>
       </c>
       <c r="T130" s="4" t="n">
-        <v>68.25</v>
+        <v>28.11</v>
       </c>
       <c r="U130" s="4" t="inlineStr"/>
       <c r="V130" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="W130" s="4" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: MA50-Rückeroberung</t>
         </is>
       </c>
       <c r="X130" s="4" t="n">
-        <v>108.01</v>
+        <v>24.29</v>
       </c>
       <c r="Y130" s="4" t="inlineStr">
         <is>
-          <t>+17.6%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="Z130" s="4" t="n">
-        <v>97.20999999999999</v>
+        <v>22.72</v>
       </c>
       <c r="AA130" s="4" t="inlineStr"/>
       <c r="AB130" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kurs UNTER MA50 — erst bei Reclaim interessant</t>
         </is>
       </c>
       <c r="AC130" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 108.00 | KP2: MA50 aktuell 71.84 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: MA150 &gt; MA200; MA200 steigt (≥1 Monat); RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 71.48 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 24.17; Kauf erst wenn Schlusskurs drüber | TT fehlt: Kurs &gt; MA150 &amp; MA200; MA150 &gt; MA200; MA200 steigt (≥1 Monat)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>FIG</t>
+          <t>FIGS</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Figma Inc</t>
+          <t>Figs Inc</t>
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>24.12</v>
+        <v>14.42</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>71.48</v>
+        <v>17.48</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>16.6</v>
+        <v>6.5</v>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>-66.3%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="G131" s="4" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>✗ 1/8</t>
+          <t>✗ 6/8</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>✓ +48%</t>
+          <t>✓ +29%</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+275%</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
@@ -15709,15 +15707,15 @@
         </is>
       </c>
       <c r="L131" s="4" t="n">
-        <v>71.55</v>
+        <v>17.5</v>
       </c>
       <c r="M131" s="4" t="inlineStr">
         <is>
-          <t>+196.6%</t>
+          <t>+21.4%</t>
         </is>
       </c>
       <c r="N131" s="4" t="n">
-        <v>66.48</v>
+        <v>16.26</v>
       </c>
       <c r="O131" s="4" t="inlineStr"/>
       <c r="P131" s="4" t="inlineStr">
@@ -15731,15 +15729,15 @@
         </is>
       </c>
       <c r="R131" s="4" t="n">
-        <v>31.23</v>
+        <v>15.75</v>
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>+29.5%</t>
+          <t>+9.2%</t>
         </is>
       </c>
       <c r="T131" s="4" t="n">
-        <v>28.11</v>
+        <v>14.18</v>
       </c>
       <c r="U131" s="4" t="inlineStr"/>
       <c r="V131" s="4" t="inlineStr">
@@ -15749,73 +15747,73 @@
       </c>
       <c r="W131" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Rückeroberung</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="X131" s="4" t="n">
-        <v>24.29</v>
+        <v>12.23</v>
       </c>
       <c r="Y131" s="4" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z131" s="4" t="n">
-        <v>22.72</v>
+        <v>11.56</v>
       </c>
       <c r="AA131" s="4" t="inlineStr"/>
       <c r="AB131" s="4" t="inlineStr">
         <is>
-          <t>Kurs UNTER MA50 — erst bei Reclaim interessant</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="AC131" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 71.48 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 24.17; Kauf erst wenn Schlusskurs drüber | TT fehlt: Kurs &gt; MA150 &amp; MA200; MA150 &gt; MA200; MA200 steigt (≥1 Monat)</t>
+          <t>KP1: 52W-Hoch 17.48 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 12.17 (nur bei intaktem Trend nutzen) | TT fehlt: MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>FIGS</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Figs Inc</t>
+          <t>Frontline Plc</t>
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>14.42</v>
+        <v>46.12</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>17.48</v>
+        <v>47.04</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>6.5</v>
+        <v>20.47</v>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="G132" s="4" t="n">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>✗ 6/8</t>
+          <t>✗ 7/8</t>
         </is>
       </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
-          <t>✓ +29%</t>
+          <t>✓ +96%</t>
         </is>
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
-          <t>+275%</t>
+          <t>+750%</t>
         </is>
       </c>
       <c r="K132" s="4" t="inlineStr">
@@ -15824,15 +15822,15 @@
         </is>
       </c>
       <c r="L132" s="4" t="n">
-        <v>17.5</v>
+        <v>47.09</v>
       </c>
       <c r="M132" s="4" t="inlineStr">
         <is>
-          <t>+21.4%</t>
+          <t>+2.1%</t>
         </is>
       </c>
       <c r="N132" s="4" t="n">
-        <v>16.26</v>
+        <v>43.75</v>
       </c>
       <c r="O132" s="4" t="inlineStr"/>
       <c r="P132" s="4" t="inlineStr">
@@ -15842,95 +15840,95 @@
       </c>
       <c r="Q132" s="4" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="R132" s="4" t="n">
-        <v>15.75</v>
+        <v>40.03</v>
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>+9.2%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="T132" s="4" t="n">
-        <v>14.18</v>
+        <v>37.83</v>
       </c>
       <c r="U132" s="4" t="inlineStr"/>
       <c r="V132" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="W132" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="X132" s="4" t="n">
-        <v>12.23</v>
+        <v>47.05</v>
       </c>
       <c r="Y132" s="4" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>+2.0%</t>
         </is>
       </c>
       <c r="Z132" s="4" t="n">
-        <v>11.56</v>
+        <v>42.35</v>
       </c>
       <c r="AA132" s="4" t="inlineStr"/>
       <c r="AB132" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="AC132" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 17.48 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 12.17 (nur bei intaktem Trend nutzen) | TT fehlt: MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 47.04 | KP2: MA50 aktuell 39.83 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Frontline Plc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>46.12</v>
+        <v>20.59</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>47.04</v>
+        <v>34.82</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>20.47</v>
+        <v>7.28</v>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-40.9%</t>
         </is>
       </c>
       <c r="G133" s="4" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>✗ 7/8</t>
+          <t>✗ 4/8</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>✓ +96%</t>
+          <t>✗ +23%</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>+750%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
@@ -15939,15 +15937,15 @@
         </is>
       </c>
       <c r="L133" s="4" t="n">
-        <v>47.09</v>
+        <v>34.85</v>
       </c>
       <c r="M133" s="4" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+69.3%</t>
         </is>
       </c>
       <c r="N133" s="4" t="n">
-        <v>43.75</v>
+        <v>32.38</v>
       </c>
       <c r="O133" s="4" t="inlineStr"/>
       <c r="P133" s="4" t="inlineStr">
@@ -15957,95 +15955,95 @@
       </c>
       <c r="Q133" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="R133" s="4" t="n">
-        <v>40.03</v>
+        <v>30.7</v>
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>+49.1%</t>
         </is>
       </c>
       <c r="T133" s="4" t="n">
-        <v>37.83</v>
+        <v>27.63</v>
       </c>
       <c r="U133" s="4" t="inlineStr"/>
       <c r="V133" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="W133" s="4" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: MA50-Rückeroberung</t>
         </is>
       </c>
       <c r="X133" s="4" t="n">
-        <v>47.05</v>
+        <v>22.31</v>
       </c>
       <c r="Y133" s="4" t="inlineStr">
         <is>
-          <t>+2.0%</t>
+          <t>+8.4%</t>
         </is>
       </c>
       <c r="Z133" s="4" t="n">
-        <v>42.35</v>
+        <v>20.87</v>
       </c>
       <c r="AA133" s="4" t="inlineStr"/>
       <c r="AB133" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kurs UNTER MA50 — erst bei Reclaim interessant</t>
         </is>
       </c>
       <c r="AC133" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 47.04 | KP2: MA50 aktuell 39.83 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 34.82 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 22.20; Kauf erst wenn Schlusskurs drüber | TT fehlt: Kurs &gt; MA150 &amp; MA200; Kurs &gt; MA50; ≤25 % unter 52W-Hoch</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>FUTU</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Futu Holdings Ltd ADR</t>
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>20.59</v>
+        <v>121.75</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>34.82</v>
+        <v>202.53</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>7.28</v>
+        <v>80.5</v>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-39.9%</t>
         </is>
       </c>
       <c r="G134" s="4" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>✗ 4/8</t>
+          <t>✗ 2/8</t>
         </is>
       </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
-          <t>✗ +23%</t>
+          <t>✓ +36%</t>
         </is>
       </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+43%</t>
         </is>
       </c>
       <c r="K134" s="4" t="inlineStr">
@@ -16054,15 +16052,15 @@
         </is>
       </c>
       <c r="L134" s="4" t="n">
-        <v>34.85</v>
+        <v>202.73</v>
       </c>
       <c r="M134" s="4" t="inlineStr">
         <is>
-          <t>+69.3%</t>
+          <t>+66.5%</t>
         </is>
       </c>
       <c r="N134" s="4" t="n">
-        <v>32.38</v>
+        <v>188.35</v>
       </c>
       <c r="O134" s="4" t="inlineStr"/>
       <c r="P134" s="4" t="inlineStr">
@@ -16076,15 +16074,15 @@
         </is>
       </c>
       <c r="R134" s="4" t="n">
-        <v>30.7</v>
+        <v>128.44</v>
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>+49.1%</t>
+          <t>+5.5%</t>
         </is>
       </c>
       <c r="T134" s="4" t="n">
-        <v>27.63</v>
+        <v>115.6</v>
       </c>
       <c r="U134" s="4" t="inlineStr"/>
       <c r="V134" s="4" t="inlineStr">
@@ -16094,73 +16092,73 @@
       </c>
       <c r="W134" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Rückeroberung</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="X134" s="4" t="n">
-        <v>22.31</v>
+        <v>107.06</v>
       </c>
       <c r="Y134" s="4" t="inlineStr">
         <is>
-          <t>+8.4%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="Z134" s="4" t="n">
-        <v>20.87</v>
+        <v>101.2</v>
       </c>
       <c r="AA134" s="4" t="inlineStr"/>
       <c r="AB134" s="4" t="inlineStr">
         <is>
-          <t>Kurs UNTER MA50 — erst bei Reclaim interessant</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="AC134" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 34.82 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 22.20; Kauf erst wenn Schlusskurs drüber | TT fehlt: Kurs &gt; MA150 &amp; MA200; Kurs &gt; MA50; ≤25 % unter 52W-Hoch</t>
+          <t>KP1: 52W-Hoch 202.53 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 106.52 (nur bei intaktem Trend nutzen) | TT fehlt: Kurs &gt; MA150 &amp; MA200; MA150 &gt; MA200; MA200 steigt (≥1 Monat)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>FUTU</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Futu Holdings Ltd ADR</t>
+          <t>GigaCloud Technology Inc</t>
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>121.75</v>
+        <v>51.75</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>202.53</v>
+        <v>56.27</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>80.5</v>
+        <v>25.39</v>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>-39.9%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="G135" s="4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>✗ 2/8</t>
+          <t>✗ 7/8</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>✓ +36%</t>
+          <t>✓ +28%</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>+43%</t>
+          <t>+28%</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
@@ -16169,15 +16167,15 @@
         </is>
       </c>
       <c r="L135" s="4" t="n">
-        <v>202.73</v>
+        <v>56.33</v>
       </c>
       <c r="M135" s="4" t="inlineStr">
         <is>
-          <t>+66.5%</t>
+          <t>+8.9%</t>
         </is>
       </c>
       <c r="N135" s="4" t="n">
-        <v>188.35</v>
+        <v>52.33</v>
       </c>
       <c r="O135" s="4" t="inlineStr"/>
       <c r="P135" s="4" t="inlineStr">
@@ -16191,15 +16189,15 @@
         </is>
       </c>
       <c r="R135" s="4" t="n">
-        <v>128.44</v>
+        <v>53.72</v>
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>+5.5%</t>
+          <t>+3.8%</t>
         </is>
       </c>
       <c r="T135" s="4" t="n">
-        <v>115.6</v>
+        <v>48.35</v>
       </c>
       <c r="U135" s="4" t="inlineStr"/>
       <c r="V135" s="4" t="inlineStr">
@@ -16213,15 +16211,15 @@
         </is>
       </c>
       <c r="X135" s="4" t="n">
-        <v>107.06</v>
+        <v>43.68</v>
       </c>
       <c r="Y135" s="4" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z135" s="4" t="n">
-        <v>101.2</v>
+        <v>41.29</v>
       </c>
       <c r="AA135" s="4" t="inlineStr"/>
       <c r="AB135" s="4" t="inlineStr">
@@ -16231,51 +16229,51 @@
       </c>
       <c r="AC135" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 202.53 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 106.52 (nur bei intaktem Trend nutzen) | TT fehlt: Kurs &gt; MA150 &amp; MA200; MA150 &gt; MA200; MA200 steigt (≥1 Monat)</t>
+          <t>KP1: 52W-Hoch 56.27 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 43.46 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>GLBE</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>GigaCloud Technology Inc</t>
+          <t>Global E Online Ltd</t>
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>51.75</v>
+        <v>38.37</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>56.27</v>
+        <v>43.99</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>25.39</v>
+        <v>26.84</v>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="G136" s="4" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>✗ 7/8</t>
+          <t>✗ 5/8</t>
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>✓ +28%</t>
+          <t>✓ +39%</t>
         </is>
       </c>
       <c r="J136" s="4" t="inlineStr">
         <is>
-          <t>+28%</t>
+          <t>+350%</t>
         </is>
       </c>
       <c r="K136" s="4" t="inlineStr">
@@ -16284,15 +16282,15 @@
         </is>
       </c>
       <c r="L136" s="4" t="n">
-        <v>56.33</v>
+        <v>44.03</v>
       </c>
       <c r="M136" s="4" t="inlineStr">
         <is>
-          <t>+8.9%</t>
+          <t>+14.8%</t>
         </is>
       </c>
       <c r="N136" s="4" t="n">
-        <v>52.33</v>
+        <v>40.91</v>
       </c>
       <c r="O136" s="4" t="inlineStr"/>
       <c r="P136" s="4" t="inlineStr">
@@ -16302,95 +16300,95 @@
       </c>
       <c r="Q136" s="4" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: MA50-Rückeroberung</t>
         </is>
       </c>
       <c r="R136" s="4" t="n">
-        <v>53.72</v>
+        <v>39</v>
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>+3.8%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="T136" s="4" t="n">
-        <v>48.35</v>
+        <v>36.47</v>
       </c>
       <c r="U136" s="4" t="inlineStr"/>
       <c r="V136" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kurs UNTER MA50 — erst bei Reclaim interessant</t>
         </is>
       </c>
       <c r="W136" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="X136" s="4" t="n">
-        <v>43.68</v>
+        <v>44</v>
       </c>
       <c r="Y136" s="4" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>+14.7%</t>
         </is>
       </c>
       <c r="Z136" s="4" t="n">
-        <v>41.29</v>
+        <v>39.6</v>
       </c>
       <c r="AA136" s="4" t="inlineStr"/>
       <c r="AB136" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="AC136" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 56.27 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 43.46 (nur bei intaktem Trend nutzen) | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 43.99 | KP2: MA50 aktuell 38.80; Kauf erst wenn Schlusskurs drüber | KP3: Hoch der letzten 20 Handelstage | TT fehlt: MA150 &gt; MA200; Kurs &gt; MA50; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>GLBE</t>
+          <t>HSHP</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Global E Online Ltd</t>
+          <t>Himalaya Shipping Ltd</t>
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>38.37</v>
+        <v>18.35</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>43.99</v>
+        <v>18.72</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>26.84</v>
+        <v>7.37</v>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="G137" s="4" t="n">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>✗ 5/8</t>
+          <t>✗ 7/8</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>✓ +39%</t>
+          <t>✓ +80%</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>+350%</t>
+          <t>+2500%</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
@@ -16399,15 +16397,15 @@
         </is>
       </c>
       <c r="L137" s="4" t="n">
-        <v>44.03</v>
+        <v>18.74</v>
       </c>
       <c r="M137" s="4" t="inlineStr">
         <is>
-          <t>+14.8%</t>
+          <t>+2.1%</t>
         </is>
       </c>
       <c r="N137" s="4" t="n">
-        <v>40.91</v>
+        <v>17.41</v>
       </c>
       <c r="O137" s="4" t="inlineStr"/>
       <c r="P137" s="4" t="inlineStr">
@@ -16417,24 +16415,24 @@
       </c>
       <c r="Q137" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Rückeroberung</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="R137" s="4" t="n">
-        <v>39</v>
+        <v>15.67</v>
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="T137" s="4" t="n">
-        <v>36.47</v>
+        <v>14.81</v>
       </c>
       <c r="U137" s="4" t="inlineStr"/>
       <c r="V137" s="4" t="inlineStr">
         <is>
-          <t>Kurs UNTER MA50 — erst bei Reclaim interessant</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="W137" s="4" t="inlineStr">
@@ -16443,15 +16441,15 @@
         </is>
       </c>
       <c r="X137" s="4" t="n">
-        <v>44</v>
+        <v>18.73</v>
       </c>
       <c r="Y137" s="4" t="inlineStr">
         <is>
-          <t>+14.7%</t>
+          <t>+2.1%</t>
         </is>
       </c>
       <c r="Z137" s="4" t="n">
-        <v>39.6</v>
+        <v>16.86</v>
       </c>
       <c r="AA137" s="4" t="inlineStr"/>
       <c r="AB137" s="4" t="inlineStr">
@@ -16461,37 +16459,37 @@
       </c>
       <c r="AC137" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 43.99 | KP2: MA50 aktuell 38.80; Kauf erst wenn Schlusskurs drüber | KP3: Hoch der letzten 20 Handelstage | TT fehlt: MA150 &gt; MA200; Kurs &gt; MA50; RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 18.72 | KP2: MA50 aktuell 15.59 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>HSHP</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Himalaya Shipping Ltd</t>
+          <t>Imax Corp</t>
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>18.35</v>
+        <v>51.64</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>18.72</v>
+        <v>55.57</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>7.37</v>
+        <v>28.93</v>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="G138" s="4" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
@@ -16500,12 +16498,12 @@
       </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>✓ +80%</t>
+          <t>✗ +12%</t>
         </is>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
-          <t>+2500%</t>
+          <t>+35%</t>
         </is>
       </c>
       <c r="K138" s="4" t="inlineStr">
@@ -16514,15 +16512,15 @@
         </is>
       </c>
       <c r="L138" s="4" t="n">
-        <v>18.74</v>
+        <v>55.63</v>
       </c>
       <c r="M138" s="4" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+7.7%</t>
         </is>
       </c>
       <c r="N138" s="4" t="n">
-        <v>17.41</v>
+        <v>51.68</v>
       </c>
       <c r="O138" s="4" t="inlineStr"/>
       <c r="P138" s="4" t="inlineStr">
@@ -16536,15 +16534,15 @@
         </is>
       </c>
       <c r="R138" s="4" t="n">
-        <v>15.67</v>
+        <v>46.62</v>
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="T138" s="4" t="n">
-        <v>14.81</v>
+        <v>44.07</v>
       </c>
       <c r="U138" s="4" t="inlineStr"/>
       <c r="V138" s="4" t="inlineStr">
@@ -16558,15 +16556,15 @@
         </is>
       </c>
       <c r="X138" s="4" t="n">
-        <v>18.73</v>
+        <v>55.58</v>
       </c>
       <c r="Y138" s="4" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+7.6%</t>
         </is>
       </c>
       <c r="Z138" s="4" t="n">
-        <v>16.86</v>
+        <v>50.03</v>
       </c>
       <c r="AA138" s="4" t="inlineStr"/>
       <c r="AB138" s="4" t="inlineStr">
@@ -16576,51 +16574,51 @@
       </c>
       <c r="AC138" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 18.72 | KP2: MA50 aktuell 15.59 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 55.57 | KP2: MA50 aktuell 46.39 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>INSM</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Imax Corp</t>
+          <t>Insmed Inc</t>
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>51.64</v>
+        <v>126.29</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>55.57</v>
+        <v>212.75</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>28.93</v>
+        <v>90.39</v>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-40.6%</t>
         </is>
       </c>
       <c r="G139" s="4" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>✗ 7/8</t>
+          <t>✗ 2/8</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>✗ +12%</t>
+          <t>✓ +296%</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>+35%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
@@ -16629,15 +16627,15 @@
         </is>
       </c>
       <c r="L139" s="4" t="n">
-        <v>55.63</v>
+        <v>212.96</v>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>+7.7%</t>
+          <t>+68.6%</t>
         </is>
       </c>
       <c r="N139" s="4" t="n">
-        <v>51.68</v>
+        <v>197.86</v>
       </c>
       <c r="O139" s="4" t="inlineStr"/>
       <c r="P139" s="4" t="inlineStr">
@@ -16647,95 +16645,95 @@
       </c>
       <c r="Q139" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="R139" s="4" t="n">
-        <v>46.62</v>
+        <v>135.51</v>
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>+7.3%</t>
         </is>
       </c>
       <c r="T139" s="4" t="n">
-        <v>44.07</v>
+        <v>121.96</v>
       </c>
       <c r="U139" s="4" t="inlineStr"/>
       <c r="V139" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="W139" s="4" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="X139" s="4" t="n">
-        <v>55.58</v>
+        <v>116.27</v>
       </c>
       <c r="Y139" s="4" t="inlineStr">
         <is>
-          <t>+7.6%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="Z139" s="4" t="n">
-        <v>50.03</v>
+        <v>109.91</v>
       </c>
       <c r="AA139" s="4" t="inlineStr"/>
       <c r="AB139" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="AC139" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 55.57 | KP2: MA50 aktuell 46.39 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 212.75 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 115.69 (nur bei intaktem Trend nutzen) | TT fehlt: Kurs &gt; MA150 &amp; MA200; MA150 &gt; MA200; MA200 steigt (≥1 Monat)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>INSM</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>Insmed Inc</t>
+          <t>Ethos Technologies Inc</t>
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>126.29</v>
+        <v>39.85</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>212.75</v>
+        <v>40.97</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>90.39</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="G140" s="4" t="n">
-        <v>7</v>
+        <v>96</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>✗ 2/8</t>
+          <t>✗ 0/8</t>
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>✓ +296%</t>
+          <t>✓ +113%</t>
         </is>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>-5%</t>
         </is>
       </c>
       <c r="K140" s="4" t="inlineStr">
@@ -16744,15 +16742,15 @@
         </is>
       </c>
       <c r="L140" s="4" t="n">
-        <v>212.96</v>
+        <v>41.01</v>
       </c>
       <c r="M140" s="4" t="inlineStr">
         <is>
-          <t>+68.6%</t>
+          <t>+2.9%</t>
         </is>
       </c>
       <c r="N140" s="4" t="n">
-        <v>197.86</v>
+        <v>38.1</v>
       </c>
       <c r="O140" s="4" t="inlineStr"/>
       <c r="P140" s="4" t="inlineStr">
@@ -16762,95 +16760,95 @@
       </c>
       <c r="Q140" s="4" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="R140" s="4" t="n">
-        <v>135.51</v>
+        <v>26.84</v>
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>+7.3%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T140" s="4" t="n">
-        <v>121.96</v>
+        <v>25.37</v>
       </c>
       <c r="U140" s="4" t="inlineStr"/>
       <c r="V140" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="W140" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="X140" s="4" t="n">
-        <v>116.27</v>
+        <v>40.98</v>
       </c>
       <c r="Y140" s="4" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>+2.8%</t>
         </is>
       </c>
       <c r="Z140" s="4" t="n">
-        <v>109.91</v>
+        <v>36.89</v>
       </c>
       <c r="AA140" s="4" t="inlineStr"/>
       <c r="AB140" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="AC140" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 212.75 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 115.69 (nur bei intaktem Trend nutzen) | TT fehlt: Kurs &gt; MA150 &amp; MA200; MA150 &gt; MA200; MA200 steigt (≥1 Monat)</t>
+          <t>KP1: 52W-Hoch 40.97 | KP2: MA50 aktuell 26.71 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: Zu wenig Historie für MA200</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>MSGE</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Ethos Technologies Inc</t>
+          <t>Madison Square Garden Entertainment Corp</t>
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>39.85</v>
+        <v>77.41</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>40.97</v>
+        <v>90.41</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>9.449999999999999</v>
+        <v>40.29</v>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="G141" s="4" t="n">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>✗ 0/8</t>
+          <t>✗ 6/8</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>✓ +113%</t>
+          <t>✓ +27%</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
@@ -16859,15 +16857,15 @@
         </is>
       </c>
       <c r="L141" s="4" t="n">
-        <v>41.01</v>
+        <v>90.5</v>
       </c>
       <c r="M141" s="4" t="inlineStr">
         <is>
-          <t>+2.9%</t>
+          <t>+16.9%</t>
         </is>
       </c>
       <c r="N141" s="4" t="n">
-        <v>38.1</v>
+        <v>84.08</v>
       </c>
       <c r="O141" s="4" t="inlineStr"/>
       <c r="P141" s="4" t="inlineStr">
@@ -16877,24 +16875,24 @@
       </c>
       <c r="Q141" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: MA50-Rückeroberung</t>
         </is>
       </c>
       <c r="R141" s="4" t="n">
-        <v>26.84</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="T141" s="4" t="n">
-        <v>25.37</v>
+        <v>73.52</v>
       </c>
       <c r="U141" s="4" t="inlineStr"/>
       <c r="V141" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kurs UNTER MA50 — erst bei Reclaim interessant</t>
         </is>
       </c>
       <c r="W141" s="4" t="inlineStr">
@@ -16903,15 +16901,15 @@
         </is>
       </c>
       <c r="X141" s="4" t="n">
-        <v>40.98</v>
+        <v>90.42</v>
       </c>
       <c r="Y141" s="4" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>+16.8%</t>
         </is>
       </c>
       <c r="Z141" s="4" t="n">
-        <v>36.89</v>
+        <v>81.38</v>
       </c>
       <c r="AA141" s="4" t="inlineStr"/>
       <c r="AB141" s="4" t="inlineStr">
@@ -16921,37 +16919,37 @@
       </c>
       <c r="AC141" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 40.97 | KP2: MA50 aktuell 26.71 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: Zu wenig Historie für MA200</t>
+          <t>KP1: 52W-Hoch 90.41 | KP2: MA50 aktuell 78.21; Kauf erst wenn Schlusskurs drüber | KP3: Hoch der letzten 20 Handelstage | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>MSGE</t>
+          <t>MTDR</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Madison Square Garden Entertainment Corp</t>
+          <t>Matador Resources Co</t>
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>77.41</v>
+        <v>59.15</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>90.41</v>
+        <v>66.84</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>40.29</v>
+        <v>37.14</v>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="G142" s="4" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
@@ -16965,7 +16963,7 @@
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+161%</t>
         </is>
       </c>
       <c r="K142" s="4" t="inlineStr">
@@ -16974,15 +16972,15 @@
         </is>
       </c>
       <c r="L142" s="4" t="n">
-        <v>90.5</v>
+        <v>66.91</v>
       </c>
       <c r="M142" s="4" t="inlineStr">
         <is>
-          <t>+16.9%</t>
+          <t>+13.1%</t>
         </is>
       </c>
       <c r="N142" s="4" t="n">
-        <v>84.08</v>
+        <v>62.16</v>
       </c>
       <c r="O142" s="4" t="inlineStr"/>
       <c r="P142" s="4" t="inlineStr">
@@ -16992,81 +16990,81 @@
       </c>
       <c r="Q142" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Rückeroberung</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="R142" s="4" t="n">
-        <v>78.59999999999999</v>
+        <v>60.39</v>
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>+1.5%</t>
+          <t>+2.1%</t>
         </is>
       </c>
       <c r="T142" s="4" t="n">
-        <v>73.52</v>
+        <v>54.36</v>
       </c>
       <c r="U142" s="4" t="inlineStr"/>
       <c r="V142" s="4" t="inlineStr">
         <is>
-          <t>Kurs UNTER MA50 — erst bei Reclaim interessant</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="W142" s="4" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="X142" s="4" t="n">
-        <v>90.42</v>
+        <v>53.2</v>
       </c>
       <c r="Y142" s="4" t="inlineStr">
         <is>
-          <t>+16.8%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="Z142" s="4" t="n">
-        <v>81.38</v>
+        <v>50.29</v>
       </c>
       <c r="AA142" s="4" t="inlineStr"/>
       <c r="AB142" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="AC142" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 90.41 | KP2: MA50 aktuell 78.21; Kauf erst wenn Schlusskurs drüber | KP3: Hoch der letzten 20 Handelstage | TT fehlt: Kurs &gt; MA50; RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 66.84 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 52.93 (nur bei intaktem Trend nutzen) | TT fehlt: MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>MTDR</t>
+          <t>NOG</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Matador Resources Co</t>
+          <t>Northern Oil and Gas Inc</t>
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>59.15</v>
+        <v>25.92</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>66.84</v>
+        <v>31.17</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>37.14</v>
+        <v>17.18</v>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="G143" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -17075,12 +17073,12 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>✓ +27%</t>
+          <t>✗ +16%</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>+161%</t>
+          <t>+119%</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
@@ -17089,15 +17087,15 @@
         </is>
       </c>
       <c r="L143" s="4" t="n">
-        <v>66.91</v>
+        <v>31.2</v>
       </c>
       <c r="M143" s="4" t="inlineStr">
         <is>
-          <t>+13.1%</t>
+          <t>+20.4%</t>
         </is>
       </c>
       <c r="N143" s="4" t="n">
-        <v>62.16</v>
+        <v>28.99</v>
       </c>
       <c r="O143" s="4" t="inlineStr"/>
       <c r="P143" s="4" t="inlineStr">
@@ -17111,15 +17109,15 @@
         </is>
       </c>
       <c r="R143" s="4" t="n">
-        <v>60.39</v>
+        <v>27.36</v>
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+5.6%</t>
         </is>
       </c>
       <c r="T143" s="4" t="n">
-        <v>54.36</v>
+        <v>24.63</v>
       </c>
       <c r="U143" s="4" t="inlineStr"/>
       <c r="V143" s="4" t="inlineStr">
@@ -17133,15 +17131,15 @@
         </is>
       </c>
       <c r="X143" s="4" t="n">
-        <v>53.2</v>
+        <v>22.38</v>
       </c>
       <c r="Y143" s="4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="Z143" s="4" t="n">
-        <v>50.29</v>
+        <v>21.16</v>
       </c>
       <c r="AA143" s="4" t="inlineStr"/>
       <c r="AB143" s="4" t="inlineStr">
@@ -17151,51 +17149,51 @@
       </c>
       <c r="AC143" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 66.84 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 52.93 (nur bei intaktem Trend nutzen) | TT fehlt: MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 31.17 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 22.27 (nur bei intaktem Trend nutzen) | TT fehlt: MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>NOG</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Northern Oil and Gas Inc</t>
+          <t>Oceaneering International Inc</t>
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>25.92</v>
+        <v>51.4</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>31.17</v>
+        <v>54.25</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>17.18</v>
+        <v>22.02</v>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="G144" s="4" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>✗ 6/8</t>
+          <t>✗ 7/8</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
-          <t>✗ +16%</t>
+          <t>✗ +10%</t>
         </is>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>+119%</t>
+          <t>+20%</t>
         </is>
       </c>
       <c r="K144" s="4" t="inlineStr">
@@ -17204,15 +17202,15 @@
         </is>
       </c>
       <c r="L144" s="4" t="n">
-        <v>31.2</v>
+        <v>54.3</v>
       </c>
       <c r="M144" s="4" t="inlineStr">
         <is>
-          <t>+20.4%</t>
+          <t>+5.6%</t>
         </is>
       </c>
       <c r="N144" s="4" t="n">
-        <v>28.99</v>
+        <v>50.45</v>
       </c>
       <c r="O144" s="4" t="inlineStr"/>
       <c r="P144" s="4" t="inlineStr">
@@ -17222,81 +17220,81 @@
       </c>
       <c r="Q144" s="4" t="inlineStr">
         <is>
-          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="R144" s="4" t="n">
-        <v>27.36</v>
+        <v>47.57</v>
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T144" s="4" t="n">
-        <v>24.63</v>
+        <v>44.97</v>
       </c>
       <c r="U144" s="4" t="inlineStr"/>
       <c r="V144" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Konsolidierungs-Pivot</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="W144" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: 20-Tage-Hoch (Pivot)</t>
         </is>
       </c>
       <c r="X144" s="4" t="n">
-        <v>22.38</v>
+        <v>54.26</v>
       </c>
       <c r="Y144" s="4" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>+5.6%</t>
         </is>
       </c>
       <c r="Z144" s="4" t="n">
-        <v>21.16</v>
+        <v>48.84</v>
       </c>
       <c r="AA144" s="4" t="inlineStr"/>
       <c r="AB144" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kein Muster — Konsolidierungs-Pivot</t>
         </is>
       </c>
       <c r="AC144" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 31.17 | KP2: Hoch der letzten 20 Handelstage | KP3: MA50 aktuell 22.27 (nur bei intaktem Trend nutzen) | TT fehlt: MA50 &gt; MA150 &amp; MA200; RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 54.25 | KP2: MA50 aktuell 47.34 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Oceaneering International Inc</t>
+          <t>Everpure Inc</t>
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>51.4</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>54.25</v>
+        <v>119.1</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>22.02</v>
+        <v>56.78</v>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="G145" s="4" t="n">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -17305,12 +17303,12 @@
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>✗ +10%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
@@ -17319,15 +17317,15 @@
         </is>
       </c>
       <c r="L145" s="4" t="n">
-        <v>54.3</v>
+        <v>119.22</v>
       </c>
       <c r="M145" s="4" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>+19.8%</t>
         </is>
       </c>
       <c r="N145" s="4" t="n">
-        <v>50.45</v>
+        <v>110.76</v>
       </c>
       <c r="O145" s="4" t="inlineStr"/>
       <c r="P145" s="4" t="inlineStr">
@@ -17341,15 +17339,15 @@
         </is>
       </c>
       <c r="R145" s="4" t="n">
-        <v>47.57</v>
+        <v>88.2</v>
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T145" s="4" t="n">
-        <v>44.97</v>
+        <v>83.37</v>
       </c>
       <c r="U145" s="4" t="inlineStr"/>
       <c r="V145" s="4" t="inlineStr">
@@ -17363,15 +17361,15 @@
         </is>
       </c>
       <c r="X145" s="4" t="n">
-        <v>54.26</v>
+        <v>119.11</v>
       </c>
       <c r="Y145" s="4" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>+19.7%</t>
         </is>
       </c>
       <c r="Z145" s="4" t="n">
-        <v>48.84</v>
+        <v>107.2</v>
       </c>
       <c r="AA145" s="4" t="inlineStr"/>
       <c r="AB145" s="4" t="inlineStr">
@@ -17381,37 +17379,37 @@
       </c>
       <c r="AC145" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 54.25 | KP2: MA50 aktuell 47.34 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 119.10 | KP2: MA50 aktuell 87.76 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>PLPC</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Everpure Inc</t>
+          <t>Preformed Line Products Co</t>
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>99.51000000000001</v>
+        <v>398.45</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>119.1</v>
+        <v>504.69</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>56.78</v>
+        <v>184.02</v>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="G146" s="4" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
@@ -17420,12 +17418,12 @@
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>✓ +25%</t>
         </is>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+75%</t>
         </is>
       </c>
       <c r="K146" s="4" t="inlineStr">
@@ -17434,15 +17432,15 @@
         </is>
       </c>
       <c r="L146" s="4" t="n">
-        <v>119.22</v>
+        <v>505.19</v>
       </c>
       <c r="M146" s="4" t="inlineStr">
         <is>
-          <t>+19.8%</t>
+          <t>+26.8%</t>
         </is>
       </c>
       <c r="N146" s="4" t="n">
-        <v>110.76</v>
+        <v>469.36</v>
       </c>
       <c r="O146" s="4" t="inlineStr"/>
       <c r="P146" s="4" t="inlineStr">
@@ -17456,15 +17454,15 @@
         </is>
       </c>
       <c r="R146" s="4" t="n">
-        <v>88.2</v>
+        <v>388.97</v>
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="T146" s="4" t="n">
-        <v>83.37</v>
+        <v>367.69</v>
       </c>
       <c r="U146" s="4" t="inlineStr"/>
       <c r="V146" s="4" t="inlineStr">
@@ -17478,15 +17476,15 @@
         </is>
       </c>
       <c r="X146" s="4" t="n">
-        <v>119.11</v>
+        <v>504.7</v>
       </c>
       <c r="Y146" s="4" t="inlineStr">
         <is>
-          <t>+19.7%</t>
+          <t>+26.7%</t>
         </is>
       </c>
       <c r="Z146" s="4" t="n">
-        <v>107.2</v>
+        <v>454.23</v>
       </c>
       <c r="AA146" s="4" t="inlineStr"/>
       <c r="AB146" s="4" t="inlineStr">
@@ -17496,37 +17494,37 @@
       </c>
       <c r="AC146" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 119.10 | KP2: MA50 aktuell 87.76 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 504.69 | KP2: MA50 aktuell 387.04 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>PLPC</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Preformed Line Products Co</t>
+          <t>Permian Resources Holdings Inc</t>
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>398.45</v>
+        <v>23.36</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>504.69</v>
+        <v>24.09</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>184.02</v>
+        <v>11.92</v>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="G147" s="4" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -17535,12 +17533,12 @@
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>✓ +25%</t>
+          <t>✓ +55%</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>+75%</t>
+          <t>+233%</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
@@ -17549,15 +17547,15 @@
         </is>
       </c>
       <c r="L147" s="4" t="n">
-        <v>505.19</v>
+        <v>24.11</v>
       </c>
       <c r="M147" s="4" t="inlineStr">
         <is>
-          <t>+26.8%</t>
+          <t>+3.2%</t>
         </is>
       </c>
       <c r="N147" s="4" t="n">
-        <v>469.36</v>
+        <v>22.4</v>
       </c>
       <c r="O147" s="4" t="inlineStr"/>
       <c r="P147" s="4" t="inlineStr">
@@ -17571,15 +17569,15 @@
         </is>
       </c>
       <c r="R147" s="4" t="n">
-        <v>388.97</v>
+        <v>21.12</v>
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="T147" s="4" t="n">
-        <v>367.69</v>
+        <v>19.97</v>
       </c>
       <c r="U147" s="4" t="inlineStr"/>
       <c r="V147" s="4" t="inlineStr">
@@ -17593,15 +17591,15 @@
         </is>
       </c>
       <c r="X147" s="4" t="n">
-        <v>504.7</v>
+        <v>24.1</v>
       </c>
       <c r="Y147" s="4" t="inlineStr">
         <is>
-          <t>+26.7%</t>
+          <t>+3.2%</t>
         </is>
       </c>
       <c r="Z147" s="4" t="n">
-        <v>454.23</v>
+        <v>21.69</v>
       </c>
       <c r="AA147" s="4" t="inlineStr"/>
       <c r="AB147" s="4" t="inlineStr">
@@ -17611,51 +17609,51 @@
       </c>
       <c r="AC147" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 504.69 | KP2: MA50 aktuell 387.04 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 24.09 | KP2: MA50 aktuell 21.02 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PSQL</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Permian Resources Holdings Inc</t>
+          <t>Pasqal Holding SA</t>
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>23.36</v>
+        <v>7.96</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>24.09</v>
+        <v>24.69</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>11.92</v>
+        <v>7.42</v>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-67.8%</t>
         </is>
       </c>
       <c r="G148" s="4" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>✗ 7/8</t>
+          <t>✗ 0/8</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
-          <t>✓ +55%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>+233%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K148" s="4" t="inlineStr">
@@ -17664,15 +17662,15 @@
         </is>
       </c>
       <c r="L148" s="4" t="n">
-        <v>24.11</v>
+        <v>24.71</v>
       </c>
       <c r="M148" s="4" t="inlineStr">
         <is>
-          <t>+3.2%</t>
+          <t>+210.4%</t>
         </is>
       </c>
       <c r="N148" s="4" t="n">
-        <v>22.4</v>
+        <v>22.96</v>
       </c>
       <c r="O148" s="4" t="inlineStr"/>
       <c r="P148" s="4" t="inlineStr">
@@ -17682,24 +17680,24 @@
       </c>
       <c r="Q148" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Pullback</t>
+          <t>Fallback: MA50-Rückeroberung</t>
         </is>
       </c>
       <c r="R148" s="4" t="n">
-        <v>21.12</v>
+        <v>10.7</v>
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>+34.4%</t>
         </is>
       </c>
       <c r="T148" s="4" t="n">
-        <v>19.97</v>
+        <v>10.01</v>
       </c>
       <c r="U148" s="4" t="inlineStr"/>
       <c r="V148" s="4" t="inlineStr">
         <is>
-          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
+          <t>Kurs UNTER MA50 — erst bei Reclaim interessant</t>
         </is>
       </c>
       <c r="W148" s="4" t="inlineStr">
@@ -17708,15 +17706,15 @@
         </is>
       </c>
       <c r="X148" s="4" t="n">
-        <v>24.1</v>
+        <v>24.7</v>
       </c>
       <c r="Y148" s="4" t="inlineStr">
         <is>
-          <t>+3.2%</t>
+          <t>+210.3%</t>
         </is>
       </c>
       <c r="Z148" s="4" t="n">
-        <v>21.69</v>
+        <v>22.23</v>
       </c>
       <c r="AA148" s="4" t="inlineStr"/>
       <c r="AB148" s="4" t="inlineStr">
@@ -17726,51 +17724,51 @@
       </c>
       <c r="AC148" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 24.09 | KP2: MA50 aktuell 21.02 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
+          <t>KP1: 52W-Hoch 24.69 | KP2: MA50 aktuell 10.65; Kauf erst wenn Schlusskurs drüber | KP3: Hoch der letzten 20 Handelstage | TT fehlt: Zu wenig Historie für MA200</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>PSQL</t>
+          <t>SCCO</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Pasqal Holding SA</t>
+          <t>Southern Copper Corp</t>
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>7.96</v>
+        <v>198.76</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>24.69</v>
+        <v>220.78</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>7.42</v>
+        <v>96.16</v>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>-67.8%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="G149" s="4" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>✗ 0/8</t>
+          <t>✗ 7/8</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>✓ +41%</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>+72%</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
@@ -17779,15 +17777,15 @@
         </is>
       </c>
       <c r="L149" s="4" t="n">
-        <v>24.71</v>
+        <v>221</v>
       </c>
       <c r="M149" s="4" t="inlineStr">
         <is>
-          <t>+210.4%</t>
+          <t>+11.2%</t>
         </is>
       </c>
       <c r="N149" s="4" t="n">
-        <v>22.96</v>
+        <v>205.33</v>
       </c>
       <c r="O149" s="4" t="inlineStr"/>
       <c r="P149" s="4" t="inlineStr">
@@ -17797,24 +17795,24 @@
       </c>
       <c r="Q149" s="4" t="inlineStr">
         <is>
-          <t>Fallback: MA50-Rückeroberung</t>
+          <t>Fallback: MA50-Pullback</t>
         </is>
       </c>
       <c r="R149" s="4" t="n">
-        <v>10.7</v>
+        <v>188.25</v>
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>+34.4%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="T149" s="4" t="n">
-        <v>10.01</v>
+        <v>177.95</v>
       </c>
       <c r="U149" s="4" t="inlineStr"/>
       <c r="V149" s="4" t="inlineStr">
         <is>
-          <t>Kurs UNTER MA50 — erst bei Reclaim interessant</t>
+          <t>Kein Muster — Rücksetzer-Kauf am MA50</t>
         </is>
       </c>
       <c r="W149" s="4" t="inlineStr">
@@ -17823,15 +17821,15 @@
         </is>
       </c>
       <c r="X149" s="4" t="n">
-        <v>24.7</v>
+        <v>220.79</v>
       </c>
       <c r="Y149" s="4" t="inlineStr">
         <is>
-          <t>+210.3%</t>
+          <t>+11.1%</t>
         </is>
       </c>
       <c r="Z149" s="4" t="n">
-        <v>22.23</v>
+        <v>198.72</v>
       </c>
       <c r="AA149" s="4" t="inlineStr"/>
       <c r="AB149" s="4" t="inlineStr">
@@ -17841,7 +17839,7 @@
       </c>
       <c r="AC149" s="4" t="inlineStr">
         <is>
-          <t>KP1: 52W-Hoch 24.69 | KP2: MA50 aktuell 10.65; Kauf erst wenn Schlusskurs drüber | KP3: Hoch der letzten 20 Handelstage | TT fehlt: Zu wenig Historie für MA200</t>
+          <t>KP1: 52W-Hoch 220.78 | KP2: MA50 aktuell 187.31 (nur bei intaktem Trend nutzen) | KP3: Hoch der letzten 20 Handelstage | TT fehlt: RS-Rank ≥ 70</t>
         </is>
       </c>
     </row>
@@ -17995,7 +17993,7 @@
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>✓ +34%</t>
+          <t>✓ +35%</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
@@ -18446,7 +18444,7 @@
         </is>
       </c>
       <c r="G155" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -18690,7 +18688,7 @@
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>+988%</t>
+          <t>+990%</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
